--- a/data/trending_integrated_20261008_10.xlsx
+++ b/data/trending_integrated_20261008_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>비아트론</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7030</v>
+        <v>14430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+8.82%</t>
+          <t>'+20.35%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.31</v>
+        <v>-0.23</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6460</v>
+        <v>11990</v>
       </c>
       <c r="K2" t="n">
-        <v>6930</v>
+        <v>14330</v>
       </c>
       <c r="L2" t="n">
-        <v>8390</v>
+        <v>14430</v>
       </c>
       <c r="M2" t="n">
-        <v>6910</v>
+        <v>13070</v>
       </c>
       <c r="N2" t="n">
-        <v>0.31</v>
+        <v>4.66</v>
       </c>
       <c r="O2" t="n">
-        <v>16545442630</v>
+        <v>22183534685</v>
       </c>
       <c r="P2" t="n">
-        <v>9680</v>
+        <v>14430</v>
       </c>
       <c r="Q2" t="n">
-        <v>371</v>
+        <v>6500</v>
       </c>
       <c r="R2" t="n">
-        <v>-23000</v>
+        <v>-16000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>반기보고서 미제출 상장폐지 해소 후에도 주가 부진, 신규 주인 확정 및 재료 소멸 우려 속에 더코디 등 타 종목과의 비교.</t>
+          <t>삼성전기향 차세대 유리기판 핵심 장비 '글라스 본더' 공급 계약 체결. 동종 업체 대비 낮은 시총으로 인한 높은 상승 여력 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['상장폐지', '재료소멸', '신규 주인']</t>
+          <t>['글라스 본더', '유리기판', '삼성전기']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,77 +648,77 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>141000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4510</v>
+        <v>6890</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.81%</t>
+          <t>'+6.66%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.19</v>
+        <v>-0.31</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
         <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H3" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4430</v>
+        <v>6460</v>
       </c>
       <c r="K3" t="n">
-        <v>4650</v>
+        <v>6930</v>
       </c>
       <c r="L3" t="n">
-        <v>4855</v>
+        <v>8390</v>
       </c>
       <c r="M3" t="n">
-        <v>4255</v>
+        <v>6890</v>
       </c>
       <c r="N3" t="n">
-        <v>3.27</v>
+        <v>0.31</v>
       </c>
       <c r="O3" t="n">
-        <v>55553553495</v>
+        <v>16929070125</v>
       </c>
       <c r="P3" t="n">
-        <v>5470</v>
+        <v>9680</v>
       </c>
       <c r="Q3" t="n">
-        <v>2810</v>
+        <v>371</v>
       </c>
       <c r="R3" t="n">
-        <v>-470000</v>
+        <v>-23000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 폭등, WHO의 러시아 폐렴 상황 파악 불가 속 전염병 우려 제기. 다만 WHO는 공중보건 위험성 낮다고 발표.</t>
+          <t>신규 최대주주 확정 기대감에도 불구하고 거래량 부진 및 주가 흐름 둔화. 재료 소멸 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['전염병', 'WHO', '폐렴']</t>
+          <t>['신규 최대주주', '거래량', '재료 소멸']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
@@ -762,13 +762,13 @@
         <v>-0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>723</v>
+        <v>747</v>
       </c>
       <c r="F4" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="G4" t="n">
-        <v>1876</v>
+        <v>1949</v>
       </c>
       <c r="H4" t="n">
         <v>49.59</v>
@@ -794,7 +794,7 @@
         <v>49.71</v>
       </c>
       <c r="O4" t="n">
-        <v>1181470858000</v>
+        <v>1252223133000</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45700</v>
+        <v>4440</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.44%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.73</v>
+        <v>1.19</v>
       </c>
       <c r="E5" t="n">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>450</v>
+        <v>117</v>
       </c>
       <c r="H5" t="n">
-        <v>13.39</v>
+        <v>4.46</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>45900</v>
+        <v>4430</v>
       </c>
       <c r="K5" t="n">
-        <v>45950</v>
+        <v>4650</v>
       </c>
       <c r="L5" t="n">
-        <v>46250</v>
+        <v>4855</v>
       </c>
       <c r="M5" t="n">
-        <v>45100</v>
+        <v>4255</v>
       </c>
       <c r="N5" t="n">
-        <v>14.12</v>
+        <v>3.27</v>
       </c>
       <c r="O5" t="n">
-        <v>9901392000</v>
+        <v>57630281274</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>5470</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>2810</v>
       </c>
       <c r="R5" t="n">
-        <v>-14000</v>
+        <v>-470000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>공매도와 전환사채 이슈 속에서도 긍정적 우상향 차트 전망, FDA 임상 3상 종료 약물에 대한 기대감과 펩트론 기술 계약 해지 반사이익 예상.</t>
+          <t>미국 항생제 보유 회사 주가 폭등, WHO의 러시아 폐렴 상황 파악 불가 속 전염병 우려 제기. 다만 WHO는 공중보건 위험성 낮다고 발표.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['공매도', '임상 3상', '전환사채']</t>
+          <t>['전염병', 'WHO', '폐렴']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>266750</v>
+        <v>8260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.65%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>-0.17</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>560</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>2285</v>
+        <v>101</v>
       </c>
       <c r="H6" t="n">
-        <v>46.38</v>
+        <v>26.38</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>268500</v>
+        <v>8250</v>
       </c>
       <c r="K6" t="n">
-        <v>269500</v>
+        <v>8190</v>
       </c>
       <c r="L6" t="n">
-        <v>270000</v>
+        <v>8320</v>
       </c>
       <c r="M6" t="n">
-        <v>266000</v>
+        <v>8090</v>
       </c>
       <c r="N6" t="n">
-        <v>46.37</v>
+        <v>26.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1000971380750</v>
+        <v>7347086830</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q6" t="n">
-        <v>90200</v>
+        <v>8090</v>
       </c>
       <c r="R6" t="n">
-        <v>-246000</v>
+        <v>-164000</v>
       </c>
       <c r="S6" t="n">
-        <v>-228000</v>
+        <v>18000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자의 3분기 108조원대 역대급 영업이익에도 불구하고 주가는 하락, 정치적 책임론과 외국인 농락에 대한 불만 표출.</t>
+          <t>지속적인 주가 하락 및 경영 부실에 대한 비판과 함께, 유상증자에 대한 부정적 전망이 지배적.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부양', '국내 증시']</t>
+          <t>['주가 하락', '경영 부실', '유상증자']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19090</v>
+        <v>267250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.30%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>566</v>
       </c>
       <c r="G7" t="n">
-        <v>125</v>
+        <v>2127</v>
       </c>
       <c r="H7" t="n">
-        <v>27.68</v>
+        <v>46.38</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>19540</v>
+        <v>268500</v>
       </c>
       <c r="K7" t="n">
-        <v>19490</v>
+        <v>269500</v>
       </c>
       <c r="L7" t="n">
-        <v>19500</v>
+        <v>270000</v>
       </c>
       <c r="M7" t="n">
-        <v>19060</v>
+        <v>266000</v>
       </c>
       <c r="N7" t="n">
-        <v>27.67</v>
+        <v>46.37</v>
       </c>
       <c r="O7" t="n">
-        <v>16454970600</v>
+        <v>1105878960250</v>
       </c>
       <c r="P7" t="n">
-        <v>35350</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>18440</v>
+        <v>90200</v>
       </c>
       <c r="R7" t="n">
-        <v>-75000</v>
+        <v>-246000</v>
       </c>
       <c r="S7" t="n">
-        <v>-17000</v>
+        <v>-228000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>K조선, 중국에 글로벌 컨테이너선 수주 80% 싹쓸이 당했다는 뉴스와 함께 주가 하락세 지속, 52주 신저점 및 2만원 이탈 가능성 언급.</t>
+          <t>107조 원대 역대급 영업이익에도 불구하고 주가 하락. 정치적 책임론과 시장 시스템 붕괴에 대한 불만 고조.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['조선업', '컨테이너선', '수주']</t>
+          <t>['영업이익', '주가 하락', '정치']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>234500</v>
+        <v>45550</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.70%</t>
+          <t>'-0.76%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.65</v>
+        <v>-0.73</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G8" t="n">
-        <v>406</v>
+        <v>459</v>
       </c>
       <c r="H8" t="n">
-        <v>3.47</v>
+        <v>13.39</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>241000</v>
+        <v>45900</v>
       </c>
       <c r="K8" t="n">
-        <v>227000</v>
+        <v>45950</v>
       </c>
       <c r="L8" t="n">
-        <v>235500</v>
+        <v>46250</v>
       </c>
       <c r="M8" t="n">
-        <v>210500</v>
+        <v>45100</v>
       </c>
       <c r="N8" t="n">
-        <v>4.12</v>
+        <v>14.12</v>
       </c>
       <c r="O8" t="n">
-        <v>23903039250</v>
+        <v>10429341850</v>
       </c>
       <c r="P8" t="n">
-        <v>1233000</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>120000</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>6000</v>
+        <v>-14000</v>
       </c>
       <c r="S8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>공매도 과열 종목 지정 및 공매도 금지 조치, 캐나다 세마 출시 및 릴레이 계약 공시 임박으로 인한 상승 기대감. 돈 버는 바이오 기업으로서의 전망.</t>
+          <t>공매도와 전환사채 이슈 속에서도 긍정적 우상향 차트 전망, FDA 임상 3상 종료 약물에 대한 기대감과 펩트론 기술 계약 해지 반사이익 예상.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도 금지', '계약 공시', '바이오']</t>
+          <t>['공매도', '임상 3상', '전환사채']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16810</v>
+        <v>19085</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-2.33%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>279</v>
+        <v>127</v>
       </c>
       <c r="H9" t="n">
-        <v>9.460000000000001</v>
+        <v>27.68</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17340</v>
+        <v>19540</v>
       </c>
       <c r="K9" t="n">
-        <v>17190</v>
+        <v>19490</v>
       </c>
       <c r="L9" t="n">
-        <v>17220</v>
+        <v>19500</v>
       </c>
       <c r="M9" t="n">
-        <v>16710</v>
+        <v>19060</v>
       </c>
       <c r="N9" t="n">
-        <v>9.5</v>
+        <v>27.67</v>
       </c>
       <c r="O9" t="n">
-        <v>17292574150</v>
+        <v>17034750870</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>18440</v>
       </c>
       <c r="R9" t="n">
-        <v>35000</v>
+        <v>-75000</v>
       </c>
       <c r="S9" t="n">
-        <v>5000</v>
+        <v>-17000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>공매도와 대차해지에 대한 우려와 호소가 반복적으로 나타나지만, 구체적인 팩트나 분석 내용은 부족함.</t>
+          <t>조선업 경쟁 심화 및 수주 부진에 대한 우려와 함께, 증권사 및 시장 시스템에 대한 불신 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '주주 호소']</t>
+          <t>['조선업', '수주 부진', '시장 불신']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76700</v>
+        <v>16860</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.72%</t>
+          <t>'-2.77%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>474</v>
+        <v>281</v>
       </c>
       <c r="H10" t="n">
-        <v>22.49</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>80500</v>
+        <v>17340</v>
       </c>
       <c r="K10" t="n">
-        <v>79600</v>
+        <v>17190</v>
       </c>
       <c r="L10" t="n">
-        <v>79600</v>
+        <v>17220</v>
       </c>
       <c r="M10" t="n">
-        <v>76600</v>
+        <v>16710</v>
       </c>
       <c r="N10" t="n">
-        <v>22.59</v>
+        <v>9.5</v>
       </c>
       <c r="O10" t="n">
-        <v>71322390250</v>
+        <v>18150639200</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-83000</v>
+        <v>35000</v>
       </c>
       <c r="S10" t="n">
-        <v>-40000</v>
+        <v>5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>한미 텍사스 가스 발전 확정 소식에도 불구하고 주가는 하락세, 개인 투자자들의 재진입과 공매도 세력의 움직임 관찰.</t>
+          <t>공매도 및 대차 해지에 대한 주주들의 호소가 반복되며, 시장 참여자들의 불만이 고조되는 상황.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['가스 발전', '원전', '공매도']</t>
+          <t>['공매도', '대차해지', '호소']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7400</v>
+        <v>233000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.37%</t>
+          <t>'-3.32%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-2.03</v>
+        <v>-0.65</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F11" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>284</v>
+        <v>436</v>
       </c>
       <c r="H11" t="n">
-        <v>3.09</v>
+        <v>3.47</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7820</v>
+        <v>241000</v>
       </c>
       <c r="K11" t="n">
-        <v>8080</v>
+        <v>227000</v>
       </c>
       <c r="L11" t="n">
-        <v>8510</v>
+        <v>235500</v>
       </c>
       <c r="M11" t="n">
-        <v>7360</v>
+        <v>210500</v>
       </c>
       <c r="N11" t="n">
-        <v>5.12</v>
+        <v>4.12</v>
       </c>
       <c r="O11" t="n">
-        <v>65631037655</v>
+        <v>24764151250</v>
       </c>
       <c r="P11" t="n">
-        <v>23500</v>
+        <v>1233000</v>
       </c>
       <c r="Q11" t="n">
-        <v>2890</v>
+        <v>120000</v>
       </c>
       <c r="R11" t="n">
-        <v>-496000</v>
+        <v>6000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>건설 및 부동산 관련 내용과 함께 일부 투자자 간의 논쟁이 나타나지만, 종목의 명확한 팩트나 전망에 대한 분석은 부족함.</t>
+          <t>공매도 과열 관련 언급 및 캐나다 세마 출시 기대. 릴레이 계약 공시와 미장 바이오 섹터 동향에 따른 수급 몰림 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['부동산', '건설', '투자자 논쟁']</t>
+          <t>['공매도', '계약공시', '세마']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16970</v>
+        <v>76600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.41%</t>
+          <t>'-4.84%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.95</v>
+        <v>-0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>175</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="G12" t="n">
-        <v>241</v>
+        <v>492</v>
       </c>
       <c r="H12" t="n">
-        <v>3.97</v>
+        <v>22.49</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17940</v>
+        <v>80500</v>
       </c>
       <c r="K12" t="n">
-        <v>17770</v>
+        <v>79600</v>
       </c>
       <c r="L12" t="n">
-        <v>17940</v>
+        <v>79600</v>
       </c>
       <c r="M12" t="n">
-        <v>16900</v>
+        <v>76500</v>
       </c>
       <c r="N12" t="n">
-        <v>4.92</v>
+        <v>22.59</v>
       </c>
       <c r="O12" t="n">
-        <v>48620909550</v>
+        <v>78681863150</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>15000</v>
+        <v>-83000</v>
       </c>
       <c r="S12" t="n">
-        <v>-8000</v>
+        <v>-40000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 급락 속 대한광통신 또한 하락세, 19,000원 돌파 시점 매도에 대한 후회와 함께 적자 기업에 대한 회의적 시각.</t>
+          <t>미국발 악재와 국내 증시 상황에 대한 언급이 공존하며, 주가 하락에 대한 개인 투자자들의 답답함 표출.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '미국 증시', '적자 기업']</t>
+          <t>['원전', '주가 하락', '미국 증시']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15760</v>
+        <v>16950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.69%</t>
+          <t>'-5.52%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.44</v>
+        <v>-0.95</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>143</v>
+        <v>265</v>
       </c>
       <c r="H13" t="n">
-        <v>0.93</v>
+        <v>3.97</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16710</v>
+        <v>17940</v>
       </c>
       <c r="K13" t="n">
-        <v>16460</v>
+        <v>17770</v>
       </c>
       <c r="L13" t="n">
-        <v>17180</v>
+        <v>17940</v>
       </c>
       <c r="M13" t="n">
-        <v>14820</v>
+        <v>16900</v>
       </c>
       <c r="N13" t="n">
-        <v>2.37</v>
+        <v>4.92</v>
       </c>
       <c r="O13" t="n">
-        <v>25299918135</v>
+        <v>52326437535</v>
       </c>
       <c r="P13" t="n">
-        <v>17590</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>6320</v>
+        <v>1272</v>
       </c>
       <c r="R13" t="n">
-        <v>37000</v>
+        <v>15000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>KBS 보도 및 AI 사이버보안협의체 선정 등 양자보안 기술력 인정받았으나, 주가는 하락세. SKT와의 협력 및 개인보안 중요성 강조.</t>
+          <t>미국 광통신주 급락 및 외인·기관 매도세에 따른 주가 하락. 적자 기업에 대한 비판 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['양자보안', 'AI', '사이버보안']</t>
+          <t>['광통신', '주가 하락', '외인 매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>54100</v>
+        <v>53900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.88%</t>
+          <t>'-7.23%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="F14" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G14" t="n">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="H14" t="n">
         <v>1.32</v>
@@ -1708,13 +1708,13 @@
         <v>63800</v>
       </c>
       <c r="M14" t="n">
-        <v>53900</v>
+        <v>53400</v>
       </c>
       <c r="N14" t="n">
         <v>1.3</v>
       </c>
       <c r="O14" t="n">
-        <v>36848232700</v>
+        <v>38875459800</v>
       </c>
       <c r="P14" t="n">
         <v>63800</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4795</v>
+        <v>4825</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.97%</t>
+          <t>'-7.39%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="H15" t="n">
         <v>4.65</v>
@@ -1806,7 +1806,7 @@
         <v>4.72</v>
       </c>
       <c r="O15" t="n">
-        <v>42476555352</v>
+        <v>44330702509</v>
       </c>
       <c r="P15" t="n">
         <v>8100</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>전환사채(CB) 30억 발행으로 인한 악재 발생, 기타법인의 대량 매도 물량 400만주가 장내 매도되었고 500만주가 더 남아있어 추가 하락 우려.</t>
+          <t>전환사채 발행 및 기타법인의 대규모 매도 발생으로 인한 초대형 악재 발생. 주가 급락 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['전환사채', 'CB물량', '장내매도']</t>
+          <t>['전환사채', '대규모 매도', '악재']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,79 +1851,79 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9980</v>
+        <v>7200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-9.36%</t>
+          <t>'-7.93%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.03</v>
+        <v>-2.03</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G16" t="n">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="H16" t="n">
-        <v>5.04</v>
+        <v>3.09</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>11010</v>
+        <v>7820</v>
       </c>
       <c r="K16" t="n">
-        <v>10110</v>
+        <v>8080</v>
       </c>
       <c r="L16" t="n">
-        <v>10130</v>
+        <v>8510</v>
       </c>
       <c r="M16" t="n">
-        <v>9870</v>
+        <v>7200</v>
       </c>
       <c r="N16" t="n">
-        <v>5.01</v>
+        <v>5.12</v>
       </c>
       <c r="O16" t="n">
-        <v>3829527770</v>
+        <v>68084854545</v>
       </c>
       <c r="P16" t="n">
-        <v>15900</v>
+        <v>23500</v>
       </c>
       <c r="Q16" t="n">
-        <v>6310</v>
+        <v>2890</v>
       </c>
       <c r="R16" t="n">
-        <v>-285000</v>
+        <v>-496000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 항생제 회사 주가 급등 소식과 함께 신풍제약에 대한 기대감 표출. 케냐 에볼라 확진 소식 언급.</t>
+          <t>건설 및 부동산 관련 내용과 함께 일부 투자자 간의 논쟁이 나타나지만, 종목의 명확한 팩트나 전망에 대한 분석은 부족함.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['항생제', '에볼라', '주가']</t>
+          <t>['부동산', '건설', '투자자 논쟁']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1935,6 +1935,190 @@
         </is>
       </c>
       <c r="Z16" t="inlineStr">
+        <is>
+          <t>038500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>라온시큐어</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>15330</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-8.26%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="E17" t="n">
+        <v>43</v>
+      </c>
+      <c r="F17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G17" t="n">
+        <v>141</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>16710</v>
+      </c>
+      <c r="K17" t="n">
+        <v>16460</v>
+      </c>
+      <c r="L17" t="n">
+        <v>17180</v>
+      </c>
+      <c r="M17" t="n">
+        <v>14820</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O17" t="n">
+        <v>26467906770</v>
+      </c>
+      <c r="P17" t="n">
+        <v>17590</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6320</v>
+      </c>
+      <c r="R17" t="n">
+        <v>37000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>양자보안 기술력 및 금융 해킹 방어 성공 사례 부각. AI 사이버보안 협의체 선정 및 계약 체결 기대감 상승.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['양자보안', 'AI', '해킹 방어']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>신풍제약</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9870</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-10.35%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E18" t="n">
+        <v>73</v>
+      </c>
+      <c r="F18" t="n">
+        <v>53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>270</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>11010</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L18" t="n">
+        <v>10130</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9850</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4282422415</v>
+      </c>
+      <c r="P18" t="n">
+        <v>15900</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6310</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-285000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>미국 항생제 회사 주가 급등 소식과 함께 신풍제약에 대한 기대감 표출. 케냐 에볼라 확진 소식 언급.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['항생제', '에볼라', '주가']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>019170</t>
         </is>

--- a/data/trending_integrated_20261008_10.xlsx
+++ b/data/trending_integrated_20261008_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14430</v>
+        <v>14780</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.35%</t>
+          <t>'+23.27%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.23</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="H2" t="n">
         <v>4.43</v>
@@ -601,7 +601,7 @@
         <v>14330</v>
       </c>
       <c r="L2" t="n">
-        <v>14430</v>
+        <v>14980</v>
       </c>
       <c r="M2" t="n">
         <v>13070</v>
@@ -610,10 +610,10 @@
         <v>4.66</v>
       </c>
       <c r="O2" t="n">
-        <v>22183534685</v>
+        <v>27921875245</v>
       </c>
       <c r="P2" t="n">
-        <v>14430</v>
+        <v>14980</v>
       </c>
       <c r="Q2" t="n">
         <v>6500</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성전기향 차세대 유리기판 핵심 장비 '글라스 본더' 공급 계약 체결. 동종 업체 대비 낮은 시총으로 인한 높은 상승 여력 기대.</t>
+          <t>삼성전기향 차세대 유리기판 핵심 글라스 본더 공급 계약에 따른 비아트론의 긍정적 전망. 동종업체 대비 낮은 시가총액과 높은 성장 잠재력 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['글라스 본더', '유리기판', '삼성전기']</t>
+          <t>['유리기판', '글라스 본더', '삼성전기']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6890</v>
+        <v>6750</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.66%</t>
+          <t>'+4.49%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.31</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -696,13 +696,13 @@
         <v>8390</v>
       </c>
       <c r="M3" t="n">
-        <v>6890</v>
+        <v>6730</v>
       </c>
       <c r="N3" t="n">
         <v>0.31</v>
       </c>
       <c r="O3" t="n">
-        <v>16929070125</v>
+        <v>17787754375</v>
       </c>
       <c r="P3" t="n">
         <v>9680</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>신규 최대주주 확정 기대감에도 불구하고 거래량 부진 및 주가 흐름 둔화. 재료 소멸 가능성 언급.</t>
+          <t>관리종목 해제 및 중견기업 소속 변경에 따른 호재에 대한 기대감과 거래량 부족, 재료 소멸 가능성에 대한 우려.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['신규 최대주주', '거래량', '재료 소멸']</t>
+          <t>['관리종목 해제', '호재', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1732000</v>
+        <v>46450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.52%</t>
+          <t>'+1.20%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.12</v>
+        <v>-0.73</v>
       </c>
       <c r="E4" t="n">
-        <v>747</v>
+        <v>130</v>
       </c>
       <c r="F4" t="n">
-        <v>414</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
-        <v>1949</v>
+        <v>476</v>
       </c>
       <c r="H4" t="n">
-        <v>49.59</v>
+        <v>13.39</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1723000</v>
+        <v>45900</v>
       </c>
       <c r="K4" t="n">
-        <v>1722000</v>
+        <v>45950</v>
       </c>
       <c r="L4" t="n">
-        <v>1750000</v>
+        <v>46500</v>
       </c>
       <c r="M4" t="n">
-        <v>1722000</v>
+        <v>45100</v>
       </c>
       <c r="N4" t="n">
-        <v>49.71</v>
+        <v>14.12</v>
       </c>
       <c r="O4" t="n">
-        <v>1252223133000</v>
+        <v>12959321775</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>403000</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>-21000</v>
+        <v>-14000</v>
       </c>
       <c r="S4" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>마이크론 급등에 따른 SK하이닉스 반등 기대감 형성. 보호예수 물량 거래 및 솔리다임 관련 언급.</t>
+          <t>글로벌 3상 임상 종료 약물에 대한 기대감과 공매도 압박 속 우상향 추세 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['마이크론', '반등', '보호예수']</t>
+          <t>['공매도', '임상', '우상향']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4440</v>
+        <v>1742000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+1.10%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.19</v>
+        <v>-0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>776</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>423</v>
       </c>
       <c r="G5" t="n">
-        <v>117</v>
+        <v>2002</v>
       </c>
       <c r="H5" t="n">
-        <v>4.46</v>
+        <v>49.59</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>4430</v>
+        <v>1723000</v>
       </c>
       <c r="K5" t="n">
-        <v>4650</v>
+        <v>1722000</v>
       </c>
       <c r="L5" t="n">
-        <v>4855</v>
+        <v>1750000</v>
       </c>
       <c r="M5" t="n">
-        <v>4255</v>
+        <v>1722000</v>
       </c>
       <c r="N5" t="n">
-        <v>3.27</v>
+        <v>49.71</v>
       </c>
       <c r="O5" t="n">
-        <v>57630281274</v>
+        <v>1386440001000</v>
       </c>
       <c r="P5" t="n">
-        <v>5470</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2810</v>
+        <v>403000</v>
       </c>
       <c r="R5" t="n">
-        <v>-470000</v>
+        <v>-21000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 폭등, WHO의 러시아 폐렴 상황 파악 불가 속 전염병 우려 제기. 다만 WHO는 공중보건 위험성 낮다고 발표.</t>
+          <t>마이크론의 급등 및 2028년까지 반도체 부족 현상 전망에 따른 SK하이닉스의 상승 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['전염병', 'WHO', '폐렴']</t>
+          <t>['마이크론', '반도체 부족', '상승 기대']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8260</v>
+        <v>8290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.48%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.17</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H6" t="n">
         <v>26.38</v>
@@ -978,7 +978,7 @@
         <v>26.55</v>
       </c>
       <c r="O6" t="n">
-        <v>7347086830</v>
+        <v>7734154905</v>
       </c>
       <c r="P6" t="n">
         <v>17950</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>지속적인 주가 하락 및 경영 부실에 대한 비판과 함께, 유상증자에 대한 부정적 전망이 지배적.</t>
+          <t>나스닥 ADR 폭락 및 예상되는 천문학적 적자에 대한 우려. 경영 방식에 대한 비판과 함께 투자자들의 주의를 촉구.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가 하락', '경영 부실', '유상증자']</t>
+          <t>['ADR', '적자', '경영 방식']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>267250</v>
+        <v>267500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="G7" t="n">
-        <v>2127</v>
+        <v>2049</v>
       </c>
       <c r="H7" t="n">
         <v>46.38</v>
@@ -1070,7 +1070,7 @@
         <v>46.37</v>
       </c>
       <c r="O7" t="n">
-        <v>1105878960250</v>
+        <v>1249583300250</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>107조 원대 역대급 영업이익에도 불구하고 주가 하락. 정치적 책임론과 시장 시스템 붕괴에 대한 불만 고조.</t>
+          <t>삼성전자의 3분기 108조 원에 달하는 역대급 영업이익에도 불구하고 주가 하락세가 지속되는 것에 대한 불만과 정치적 요인으로 인한 시장 시스템 붕괴 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '정치']</t>
+          <t>['영업이익', '주가 하락', '시장 시스템']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45550</v>
+        <v>19105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.76%</t>
+          <t>'-2.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.73</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>459</v>
+        <v>146</v>
       </c>
       <c r="H8" t="n">
-        <v>13.39</v>
+        <v>27.68</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>45900</v>
+        <v>19540</v>
       </c>
       <c r="K8" t="n">
-        <v>45950</v>
+        <v>19490</v>
       </c>
       <c r="L8" t="n">
-        <v>46250</v>
+        <v>19500</v>
       </c>
       <c r="M8" t="n">
-        <v>45100</v>
+        <v>19060</v>
       </c>
       <c r="N8" t="n">
-        <v>14.12</v>
+        <v>27.67</v>
       </c>
       <c r="O8" t="n">
-        <v>10429341850</v>
+        <v>18025978100</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>18440</v>
       </c>
       <c r="R8" t="n">
-        <v>-14000</v>
+        <v>-75000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-17000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>공매도와 전환사채 이슈 속에서도 긍정적 우상향 차트 전망, FDA 임상 3상 종료 약물에 대한 기대감과 펩트론 기술 계약 해지 반사이익 예상.</t>
+          <t>조선업계 수주 소식에도 불구하고 주가 하락세가 이어지는 것에 대한 불만과 증권사 애널리스트들에 대한 불신.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '임상 3상', '전환사채']</t>
+          <t>['조선업', '주가 하락', '증권사 애널리스트']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19085</v>
+        <v>4320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.33%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01</v>
+        <v>1.19</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H9" t="n">
-        <v>27.68</v>
+        <v>4.46</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>19540</v>
+        <v>4430</v>
       </c>
       <c r="K9" t="n">
-        <v>19490</v>
+        <v>4650</v>
       </c>
       <c r="L9" t="n">
-        <v>19500</v>
+        <v>4855</v>
       </c>
       <c r="M9" t="n">
-        <v>19060</v>
+        <v>4255</v>
       </c>
       <c r="N9" t="n">
-        <v>27.67</v>
+        <v>3.27</v>
       </c>
       <c r="O9" t="n">
-        <v>17034750870</v>
+        <v>59440878804</v>
       </c>
       <c r="P9" t="n">
-        <v>35350</v>
+        <v>5470</v>
       </c>
       <c r="Q9" t="n">
-        <v>18440</v>
+        <v>2810</v>
       </c>
       <c r="R9" t="n">
-        <v>-75000</v>
+        <v>-470000</v>
       </c>
       <c r="S9" t="n">
-        <v>-17000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>조선업 경쟁 심화 및 수주 부진에 대한 우려와 함께, 증권사 및 시장 시스템에 대한 불신 제기.</t>
+          <t>미국 항생제 보유 회사 주가 폭등, WHO의 러시아 폐렴 상황 파악 불가 속 전염병 우려 제기. 다만 WHO는 공중보건 위험성 낮다고 발표.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['조선업', '수주 부진', '시장 불신']</t>
+          <t>['전염병', 'WHO', '폐렴']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1314,13 @@
         <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="H10" t="n">
         <v>9.460000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.5</v>
       </c>
       <c r="O10" t="n">
-        <v>18150639200</v>
+        <v>19553289795</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>공매도 및 대차 해지에 대한 주주들의 호소가 반복되며, 시장 참여자들의 불만이 고조되는 상황.</t>
+          <t>공매도 과열 의혹 및 대차 해지 중요성 강조. 일부 투자자들은 공매도 세력의 행위에 대한 불만을 표출하며 대차 해지를 통한 주가 방어를 호소.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '호소']</t>
+          <t>['공매도', '대차 해지', '호소']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>233000</v>
+        <v>234000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.32%</t>
+          <t>'-2.90%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="H11" t="n">
         <v>3.47</v>
@@ -1438,7 +1438,7 @@
         <v>4.12</v>
       </c>
       <c r="O11" t="n">
-        <v>24764151250</v>
+        <v>25782982250</v>
       </c>
       <c r="P11" t="n">
         <v>1233000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>공매도 과열 관련 언급 및 캐나다 세마 출시 기대. 릴레이 계약 공시와 미장 바이오 섹터 동향에 따른 수급 몰림 전망.</t>
+          <t>캐나다 세마 임상 결과 기대감 및 릴레이 계약 공시 예정, 공매도 금지 조치.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '계약공시', '세마']</t>
+          <t>['공매도', '임상', '계약공시']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76600</v>
+        <v>76800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.84%</t>
+          <t>'-4.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="F12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G12" t="n">
-        <v>492</v>
+        <v>540</v>
       </c>
       <c r="H12" t="n">
         <v>22.49</v>
@@ -1530,7 +1530,7 @@
         <v>22.59</v>
       </c>
       <c r="O12" t="n">
-        <v>78681863150</v>
+        <v>85699019050</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국발 악재와 국내 증시 상황에 대한 언급이 공존하며, 주가 하락에 대한 개인 투자자들의 답답함 표출.</t>
+          <t>미국 텍사스 가스발전 확정 소식에도 불구하고 주가 하락이 지속되는 것에 대한 실망감과 개인 투자자들의 개입에 대한 경계.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '주가 하락', '미국 증시']</t>
+          <t>['가스발전', '주가 하락', '개인 투자자']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16950</v>
+        <v>17060</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.52%</t>
+          <t>'-4.91%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.95</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="H13" t="n">
         <v>3.97</v>
@@ -1622,7 +1622,7 @@
         <v>4.92</v>
       </c>
       <c r="O13" t="n">
-        <v>52326437535</v>
+        <v>56773449805</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신주 급락 및 외인·기관 매도세에 따른 주가 하락. 적자 기업에 대한 비판 제기.</t>
+          <t>미국 광통신 주식의 급락 및 외인/기관의 매도세로 인한 주가 하락 우려. 적자 기업이라는 점과 매물대 저항에 대한 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '주가 하락', '외인 매도']</t>
+          <t>['광통신', '주가 하락', '외인/기관 매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53900</v>
+        <v>4880</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-7.23%</t>
+          <t>'-6.33%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>375</v>
+        <v>215</v>
       </c>
       <c r="H14" t="n">
-        <v>1.32</v>
+        <v>4.65</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>58100</v>
+        <v>5210</v>
       </c>
       <c r="K14" t="n">
-        <v>63200</v>
+        <v>5220</v>
       </c>
       <c r="L14" t="n">
-        <v>63800</v>
+        <v>5310</v>
       </c>
       <c r="M14" t="n">
-        <v>53400</v>
+        <v>4755</v>
       </c>
       <c r="N14" t="n">
-        <v>1.3</v>
+        <v>4.72</v>
       </c>
       <c r="O14" t="n">
-        <v>38875459800</v>
+        <v>47957857409</v>
       </c>
       <c r="P14" t="n">
-        <v>63800</v>
+        <v>8100</v>
       </c>
       <c r="Q14" t="n">
-        <v>25600</v>
+        <v>592</v>
       </c>
       <c r="R14" t="n">
-        <v>-154000</v>
+        <v>237000</v>
       </c>
       <c r="S14" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 비만주 급등 속 국내 시장 관심. 유통 물량 13%로 개미 꼬시기 의혹 제기. 불법 조작 거래 신고 주장.</t>
+          <t>전환사채 발행으로 인한 추가적인 악재 발생 가능성에 대한 우려와 주가 하락에 대한 걱정. 일부 투자자들은 긍정적인 전망을 제시.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['비만약', '유통물량', '불법거래']</t>
+          <t>['전환사채', '악재', '주가 하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4825</v>
+        <v>54350</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.39%</t>
+          <t>'-6.45%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="G15" t="n">
-        <v>203</v>
+        <v>384</v>
       </c>
       <c r="H15" t="n">
-        <v>4.65</v>
+        <v>1.32</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5210</v>
+        <v>58100</v>
       </c>
       <c r="K15" t="n">
-        <v>5220</v>
+        <v>63200</v>
       </c>
       <c r="L15" t="n">
-        <v>5310</v>
+        <v>63800</v>
       </c>
       <c r="M15" t="n">
-        <v>4755</v>
+        <v>53400</v>
       </c>
       <c r="N15" t="n">
-        <v>4.72</v>
+        <v>1.3</v>
       </c>
       <c r="O15" t="n">
-        <v>44330702509</v>
+        <v>41030361300</v>
       </c>
       <c r="P15" t="n">
-        <v>8100</v>
+        <v>63800</v>
       </c>
       <c r="Q15" t="n">
-        <v>592</v>
+        <v>25600</v>
       </c>
       <c r="R15" t="n">
-        <v>237000</v>
+        <v>-154000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 기타법인의 대규모 매도 발생으로 인한 초대형 악재 발생. 주가 급락 우려.</t>
+          <t>국내 비만약 개발 및 출시 관련 언급, 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['전환사채', '대규모 매도', '악재']</t>
+          <t>['비만약', '신약', '주가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-7.93%</t>
+          <t>'-6.65%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-2.03</v>
       </c>
       <c r="E16" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F16" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="H16" t="n">
         <v>3.09</v>
@@ -1892,13 +1892,13 @@
         <v>8510</v>
       </c>
       <c r="M16" t="n">
-        <v>7200</v>
+        <v>7170</v>
       </c>
       <c r="N16" t="n">
         <v>5.12</v>
       </c>
       <c r="O16" t="n">
-        <v>68084854545</v>
+        <v>70242471165</v>
       </c>
       <c r="P16" t="n">
         <v>23500</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15330</v>
+        <v>15500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-8.26%</t>
+          <t>'-7.24%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-1.44</v>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H17" t="n">
         <v>0.93</v>
@@ -1990,7 +1990,7 @@
         <v>2.37</v>
       </c>
       <c r="O17" t="n">
-        <v>26467906770</v>
+        <v>27086062725</v>
       </c>
       <c r="P17" t="n">
         <v>17590</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>양자보안 기술력 및 금융 해킹 방어 성공 사례 부각. AI 사이버보안 협의체 선정 및 계약 체결 기대감 상승.</t>
+          <t>AI 사이버보안 협의체 선정 및 금융권 해킹 방어 성공 사례, 계약 체결 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자보안', 'AI', '해킹 방어']</t>
+          <t>['AI', '사이버보안', '계약']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9870</v>
+        <v>9860</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-10.35%</t>
+          <t>'-10.45%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="H18" t="n">
         <v>5.04</v>
@@ -2082,7 +2082,7 @@
         <v>5.01</v>
       </c>
       <c r="O18" t="n">
-        <v>4282422415</v>
+        <v>4533609565</v>
       </c>
       <c r="P18" t="n">
         <v>15900</v>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 항생제 회사 주가 급등 소식과 함께 신풍제약에 대한 기대감 표출. 케냐 에볼라 확진 소식 언급.</t>
+          <t>미국 항생제 관련 상승세 및 케냐 에볼라 발생 관련 언급, 주가 변동성에 대한 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261008_10.xlsx
+++ b/data/trending_integrated_20261008_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>비아트론</t>
+          <t>HLB바이오스텝</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14780</v>
+        <v>6310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.27%</t>
+          <t>'+29.97%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.23</v>
+        <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="H2" t="n">
-        <v>4.43</v>
+        <v>0.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>11990</v>
+        <v>4855</v>
       </c>
       <c r="K2" t="n">
-        <v>14330</v>
+        <v>5300</v>
       </c>
       <c r="L2" t="n">
-        <v>14980</v>
+        <v>6310</v>
       </c>
       <c r="M2" t="n">
-        <v>13070</v>
+        <v>5190</v>
       </c>
       <c r="N2" t="n">
-        <v>4.66</v>
+        <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>27921875245</v>
+        <v>29901402750</v>
       </c>
       <c r="P2" t="n">
-        <v>14980</v>
+        <v>6310</v>
       </c>
       <c r="Q2" t="n">
-        <v>6500</v>
+        <v>1086</v>
       </c>
       <c r="R2" t="n">
-        <v>-16000</v>
+        <v>-65000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성전기향 차세대 유리기판 핵심 글라스 본더 공급 계약에 따른 비아트론의 긍정적 전망. 동종업체 대비 낮은 시가총액과 높은 성장 잠재력 언급.</t>
+          <t>HLB바이오스텝의 바이오 섹터 대장주 역할 기대감 및 에볼라, 페스트 창궐, 간암 FDA 승인 임박 등 다수의 호재성 뉴스에 따른 강한 상승세 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['유리기판', '글라스 본더', '삼성전기']</t>
+          <t>['바이오', '대장주', 'FDA']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>278650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>비아트론</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6750</v>
+        <v>14470</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+4.49%</t>
+          <t>'+20.68%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.31</v>
+        <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6460</v>
+        <v>11990</v>
       </c>
       <c r="K3" t="n">
-        <v>6930</v>
+        <v>14330</v>
       </c>
       <c r="L3" t="n">
-        <v>8390</v>
+        <v>14980</v>
       </c>
       <c r="M3" t="n">
-        <v>6730</v>
+        <v>13070</v>
       </c>
       <c r="N3" t="n">
-        <v>0.31</v>
+        <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>17787754375</v>
+        <v>30544117960</v>
       </c>
       <c r="P3" t="n">
-        <v>9680</v>
+        <v>14980</v>
       </c>
       <c r="Q3" t="n">
-        <v>371</v>
+        <v>6500</v>
       </c>
       <c r="R3" t="n">
-        <v>-23000</v>
+        <v>-16000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>관리종목 해제 및 중견기업 소속 변경에 따른 호재에 대한 기대감과 거래량 부족, 재료 소멸 가능성에 대한 우려.</t>
+          <t>삼성전기향 차세대 유리기판 핵심 글라스 본더 공급 계약 체결. 동종업체 대비 낮은 시가총액으로 높은 상승 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['관리종목 해제', '호재', '거래량']</t>
+          <t>['유리기판', '글라스 본더', '공급 계약']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>141000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46450</v>
+        <v>11310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.20%</t>
+          <t>'+14.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.73</v>
+        <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>476</v>
+        <v>133</v>
       </c>
       <c r="H4" t="n">
-        <v>13.39</v>
+        <v>37.45</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>45900</v>
+        <v>9880</v>
       </c>
       <c r="K4" t="n">
-        <v>45950</v>
+        <v>10030</v>
       </c>
       <c r="L4" t="n">
-        <v>46500</v>
+        <v>11540</v>
       </c>
       <c r="M4" t="n">
-        <v>45100</v>
+        <v>9850</v>
       </c>
       <c r="N4" t="n">
-        <v>14.12</v>
+        <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>12959321775</v>
+        <v>41898059605</v>
       </c>
       <c r="P4" t="n">
-        <v>69200</v>
+        <v>19150</v>
       </c>
       <c r="Q4" t="n">
-        <v>24150</v>
+        <v>3445</v>
       </c>
       <c r="R4" t="n">
-        <v>-14000</v>
+        <v>45000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>글로벌 3상 임상 종료 약물에 대한 기대감과 공매도 압박 속 우상향 추세 전망.</t>
+          <t>피노의 전구체 독점 사업권 및 매출 성장 가능성에 기반한 주가 상승 기대감. 2차전지 섹터 전반의 강세와 ETF 편입 가능성도 긍정적 요인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공매도', '임상', '우상향']</t>
+          <t>['전구체', '매출', '2차전지']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1742000</v>
+        <v>39250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.10%</t>
+          <t>'+8.43%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.12</v>
+        <v>0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>776</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>423</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>2002</v>
+        <v>82</v>
       </c>
       <c r="H5" t="n">
-        <v>49.59</v>
+        <v>31.86</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1723000</v>
+        <v>36200</v>
       </c>
       <c r="K5" t="n">
-        <v>1722000</v>
+        <v>36250</v>
       </c>
       <c r="L5" t="n">
-        <v>1750000</v>
+        <v>39850</v>
       </c>
       <c r="M5" t="n">
-        <v>1722000</v>
+        <v>36000</v>
       </c>
       <c r="N5" t="n">
-        <v>49.71</v>
+        <v>31.78</v>
       </c>
       <c r="O5" t="n">
-        <v>1386440001000</v>
+        <v>81650505600</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>45000</v>
       </c>
       <c r="Q5" t="n">
-        <v>403000</v>
+        <v>15530</v>
       </c>
       <c r="R5" t="n">
-        <v>-21000</v>
+        <v>4000</v>
       </c>
       <c r="S5" t="n">
-        <v>-5000</v>
+        <v>14000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>마이크론의 급등 및 2028년까지 반도체 부족 현상 전망에 따른 SK하이닉스의 상승 기대감.</t>
+          <t>하락장 속에서 주가 방어 성공 및 추세 전환 기대감. 외국인 순매수 및 4만원 안착 여부가 관건.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['마이크론', '반도체 부족', '상승 기대']</t>
+          <t>['추세', '외국인', '안착']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8290</v>
+        <v>6880</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.48%</t>
+          <t>'+6.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.17</v>
+        <v>-0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="H6" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>8250</v>
+        <v>6460</v>
       </c>
       <c r="K6" t="n">
-        <v>8190</v>
+        <v>6930</v>
       </c>
       <c r="L6" t="n">
-        <v>8320</v>
+        <v>8390</v>
       </c>
       <c r="M6" t="n">
-        <v>8090</v>
+        <v>6730</v>
       </c>
       <c r="N6" t="n">
-        <v>26.55</v>
+        <v>0.31</v>
       </c>
       <c r="O6" t="n">
-        <v>7734154905</v>
+        <v>17966953425</v>
       </c>
       <c r="P6" t="n">
-        <v>17950</v>
+        <v>9680</v>
       </c>
       <c r="Q6" t="n">
-        <v>8090</v>
+        <v>371</v>
       </c>
       <c r="R6" t="n">
-        <v>-164000</v>
+        <v>-23000</v>
       </c>
       <c r="S6" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>나스닥 ADR 폭락 및 예상되는 천문학적 적자에 대한 우려. 경영 방식에 대한 비판과 함께 투자자들의 주의를 촉구.</t>
+          <t>새 주인 확정 및 관리종목 해제 호재에도 주가 하락 지속. 매물대 저항 및 거래량 부족이 발목.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['ADR', '적자', '경영 방식']</t>
+          <t>['관리종목', '신규 주인', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>267500</v>
+        <v>13170</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'+4.77%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>41</v>
       </c>
       <c r="F7" t="n">
-        <v>562</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>2049</v>
+        <v>68</v>
       </c>
       <c r="H7" t="n">
-        <v>46.38</v>
+        <v>1.07</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>268500</v>
+        <v>12570</v>
       </c>
       <c r="K7" t="n">
-        <v>269500</v>
+        <v>12970</v>
       </c>
       <c r="L7" t="n">
-        <v>270000</v>
+        <v>14070</v>
       </c>
       <c r="M7" t="n">
-        <v>266000</v>
+        <v>12500</v>
       </c>
       <c r="N7" t="n">
-        <v>46.37</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>1249583300250</v>
+        <v>40140600220</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>22250</v>
       </c>
       <c r="Q7" t="n">
-        <v>90200</v>
+        <v>6000</v>
       </c>
       <c r="R7" t="n">
-        <v>-246000</v>
+        <v>-152000</v>
       </c>
       <c r="S7" t="n">
-        <v>-228000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자의 3분기 108조 원에 달하는 역대급 영업이익에도 불구하고 주가 하락세가 지속되는 것에 대한 불만과 정치적 요인으로 인한 시장 시스템 붕괴 우려.</t>
+          <t>유증 물량 정리 후 주가 반등 기대감. 비만 치료제 개발 이슈와 HLB 승인 여부가 주요 관전 포인트.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '시장 시스템']</t>
+          <t>['유증', '비만치료제', 'HLB']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19105</v>
+        <v>1743000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.23%</t>
+          <t>'+1.16%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>433</v>
       </c>
       <c r="G8" t="n">
-        <v>146</v>
+        <v>2013</v>
       </c>
       <c r="H8" t="n">
-        <v>27.68</v>
+        <v>49.59</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>19540</v>
+        <v>1723000</v>
       </c>
       <c r="K8" t="n">
-        <v>19490</v>
+        <v>1722000</v>
       </c>
       <c r="L8" t="n">
-        <v>19500</v>
+        <v>1750000</v>
       </c>
       <c r="M8" t="n">
-        <v>19060</v>
+        <v>1722000</v>
       </c>
       <c r="N8" t="n">
-        <v>27.67</v>
+        <v>49.71</v>
       </c>
       <c r="O8" t="n">
-        <v>18025978100</v>
+        <v>1486042575000</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>18440</v>
+        <v>403000</v>
       </c>
       <c r="R8" t="n">
-        <v>-75000</v>
+        <v>-21000</v>
       </c>
       <c r="S8" t="n">
-        <v>-17000</v>
+        <v>-5000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>조선업계 수주 소식에도 불구하고 주가 하락세가 이어지는 것에 대한 불만과 증권사 애널리스트들에 대한 불신.</t>
+          <t>마이크론의 급등 및 2028년까지 반도체 부족 현상 전망에 따른 SK하이닉스의 상승 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['조선업', '주가 하락', '증권사 애널리스트']</t>
+          <t>['마이크론', '반도체 부족', '상승 기대']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4320</v>
+        <v>8300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'+0.61%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.19</v>
+        <v>-0.17</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H9" t="n">
-        <v>4.46</v>
+        <v>26.38</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4430</v>
+        <v>8250</v>
       </c>
       <c r="K9" t="n">
-        <v>4650</v>
+        <v>8190</v>
       </c>
       <c r="L9" t="n">
-        <v>4855</v>
+        <v>8320</v>
       </c>
       <c r="M9" t="n">
-        <v>4255</v>
+        <v>8090</v>
       </c>
       <c r="N9" t="n">
-        <v>3.27</v>
+        <v>26.55</v>
       </c>
       <c r="O9" t="n">
-        <v>59440878804</v>
+        <v>8040823110</v>
       </c>
       <c r="P9" t="n">
-        <v>5470</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>2810</v>
+        <v>8090</v>
       </c>
       <c r="R9" t="n">
-        <v>-470000</v>
+        <v>-164000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 폭등, WHO의 러시아 폐렴 상황 파악 불가 속 전염병 우려 제기. 다만 WHO는 공중보건 위험성 낮다고 발표.</t>
+          <t>나스닥 ADR 폭락 및 회사의 고질적인 적자 문제로 인한 투자 심리 악화. 경영 능력에 대한 비판과 주가 하락 전망이 지배적.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['전염병', 'WHO', '폐렴']</t>
+          <t>['적자', '경영', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16860</v>
+        <v>45850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.77%</t>
+          <t>'-0.11%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.04</v>
+        <v>-0.73</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>301</v>
+        <v>495</v>
       </c>
       <c r="H10" t="n">
-        <v>9.460000000000001</v>
+        <v>13.39</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17340</v>
+        <v>45900</v>
       </c>
       <c r="K10" t="n">
-        <v>17190</v>
+        <v>45950</v>
       </c>
       <c r="L10" t="n">
-        <v>17220</v>
+        <v>46500</v>
       </c>
       <c r="M10" t="n">
-        <v>16710</v>
+        <v>45100</v>
       </c>
       <c r="N10" t="n">
-        <v>9.5</v>
+        <v>14.12</v>
       </c>
       <c r="O10" t="n">
-        <v>19553289795</v>
+        <v>15484529300</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>35000</v>
+        <v>-14000</v>
       </c>
       <c r="S10" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>공매도 과열 의혹 및 대차 해지 중요성 강조. 일부 투자자들은 공매도 세력의 행위에 대한 불만을 표출하며 대차 해지를 통한 주가 방어를 호소.</t>
+          <t>글로벌 3상 임상 종료 약물에 대한 기대감과 공매도 압박 속 우상향 추세 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '대차 해지', '호소']</t>
+          <t>['공매도', '임상', '우상향']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>234000</v>
+        <v>267750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.90%</t>
+          <t>'-0.28%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.65</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>103</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>563</v>
       </c>
       <c r="G11" t="n">
-        <v>452</v>
+        <v>2077</v>
       </c>
       <c r="H11" t="n">
-        <v>3.47</v>
+        <v>46.38</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>241000</v>
+        <v>268500</v>
       </c>
       <c r="K11" t="n">
-        <v>227000</v>
+        <v>269500</v>
       </c>
       <c r="L11" t="n">
-        <v>235500</v>
+        <v>270000</v>
       </c>
       <c r="M11" t="n">
-        <v>210500</v>
+        <v>266000</v>
       </c>
       <c r="N11" t="n">
-        <v>4.12</v>
+        <v>46.37</v>
       </c>
       <c r="O11" t="n">
-        <v>25782982250</v>
+        <v>1333740295750</v>
       </c>
       <c r="P11" t="n">
-        <v>1233000</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>120000</v>
+        <v>90200</v>
       </c>
       <c r="R11" t="n">
-        <v>6000</v>
+        <v>-246000</v>
       </c>
       <c r="S11" t="n">
-        <v>1000</v>
+        <v>-228000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>캐나다 세마 임상 결과 기대감 및 릴레이 계약 공시 예정, 공매도 금지 조치.</t>
+          <t>역대급 3분기 영업이익에도 불구하고 주가 하락이 지속되는 상황에 대한 불만과 정치적 책임론 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '임상', '계약공시']</t>
+          <t>['영업이익', '주가하락', '국장']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76800</v>
+        <v>19100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.60%</t>
+          <t>'-2.25%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>188</v>
+        <v>58</v>
       </c>
       <c r="F12" t="n">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>540</v>
+        <v>167</v>
       </c>
       <c r="H12" t="n">
-        <v>22.49</v>
+        <v>27.68</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>80500</v>
+        <v>19540</v>
       </c>
       <c r="K12" t="n">
-        <v>79600</v>
+        <v>19490</v>
       </c>
       <c r="L12" t="n">
-        <v>79600</v>
+        <v>19500</v>
       </c>
       <c r="M12" t="n">
-        <v>76500</v>
+        <v>19060</v>
       </c>
       <c r="N12" t="n">
-        <v>22.59</v>
+        <v>27.67</v>
       </c>
       <c r="O12" t="n">
-        <v>85699019050</v>
+        <v>18976481340</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>18440</v>
       </c>
       <c r="R12" t="n">
-        <v>-83000</v>
+        <v>-75000</v>
       </c>
       <c r="S12" t="n">
-        <v>-40000</v>
+        <v>-17000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 텍사스 가스발전 확정 소식에도 불구하고 주가 하락이 지속되는 것에 대한 실망감과 개인 투자자들의 개입에 대한 경계.</t>
+          <t>글로벌 조선업 경쟁 심화 및 수주 부진 가능성에 대한 우려로 주가 하락세 지속. 애널리스트에 대한 불신과 투자 전략 부재 지적.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['가스발전', '주가 하락', '개인 투자자']</t>
+          <t>['조선업', '수주', '신저점']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17060</v>
+        <v>16830</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.91%</t>
+          <t>'-2.94%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.95</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="H13" t="n">
-        <v>3.97</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17940</v>
+        <v>17340</v>
       </c>
       <c r="K13" t="n">
-        <v>17770</v>
+        <v>17190</v>
       </c>
       <c r="L13" t="n">
-        <v>17940</v>
+        <v>17220</v>
       </c>
       <c r="M13" t="n">
-        <v>16900</v>
+        <v>16710</v>
       </c>
       <c r="N13" t="n">
-        <v>4.92</v>
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
-        <v>56773449805</v>
+        <v>20631655150</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="S13" t="n">
-        <v>-8000</v>
+        <v>5000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신 주식의 급락 및 외인/기관의 매도세로 인한 주가 하락 우려. 적자 기업이라는 점과 매물대 저항에 대한 언급.</t>
+          <t>공매도 및 대차 해지에 대한 관심이 높으나, 실질적인 주가 부양 근거나 명확한 호재는 부족한 상황.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '주가 하락', '외인/기관 매도']</t>
+          <t>['공매도', '대차해지', '연기금']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4880</v>
+        <v>232500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.33%</t>
+          <t>'-3.53%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.65</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>215</v>
+        <v>490</v>
       </c>
       <c r="H14" t="n">
-        <v>4.65</v>
+        <v>3.47</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>5210</v>
+        <v>241000</v>
       </c>
       <c r="K14" t="n">
-        <v>5220</v>
+        <v>227000</v>
       </c>
       <c r="L14" t="n">
-        <v>5310</v>
+        <v>235500</v>
       </c>
       <c r="M14" t="n">
-        <v>4755</v>
+        <v>210500</v>
       </c>
       <c r="N14" t="n">
-        <v>4.72</v>
+        <v>4.12</v>
       </c>
       <c r="O14" t="n">
-        <v>47957857409</v>
+        <v>26686605500</v>
       </c>
       <c r="P14" t="n">
-        <v>8100</v>
+        <v>1233000</v>
       </c>
       <c r="Q14" t="n">
-        <v>592</v>
+        <v>120000</v>
       </c>
       <c r="R14" t="n">
-        <v>237000</v>
+        <v>6000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>전환사채 발행으로 인한 추가적인 악재 발생 가능성에 대한 우려와 주가 하락에 대한 걱정. 일부 투자자들은 긍정적인 전망을 제시.</t>
+          <t>공매도 과열 종목 지정 속 연기금 7일 연속 순매수. 캐나다 세마 출시 및 릴레이 계약 공시 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['전환사채', '악재', '주가 하락']</t>
+          <t>['공매도', '연기금', '계약 공시']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54350</v>
+        <v>76700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-6.45%</t>
+          <t>'-4.72%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="F15" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G15" t="n">
-        <v>384</v>
+        <v>536</v>
       </c>
       <c r="H15" t="n">
-        <v>1.32</v>
+        <v>22.49</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>58100</v>
+        <v>80500</v>
       </c>
       <c r="K15" t="n">
-        <v>63200</v>
+        <v>79600</v>
       </c>
       <c r="L15" t="n">
-        <v>63800</v>
+        <v>79600</v>
       </c>
       <c r="M15" t="n">
-        <v>53400</v>
+        <v>76500</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3</v>
+        <v>22.59</v>
       </c>
       <c r="O15" t="n">
-        <v>41030361300</v>
+        <v>91434592150</v>
       </c>
       <c r="P15" t="n">
-        <v>63800</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>25600</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-154000</v>
+        <v>-83000</v>
       </c>
       <c r="S15" t="n">
-        <v>-5000</v>
+        <v>-40000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>국내 비만약 개발 및 출시 관련 언급, 주가 하락에 대한 불만 표출.</t>
+          <t>미국 원전주 하락 영향과 더불어 국내 원전 관련 사업 진행 불확실성으로 인한 하락세 지속. 구체적인 수출 호재 언급은 있으나 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['비만약', '신약', '주가']</t>
+          <t>['원전', '수출', '하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7300</v>
+        <v>4220</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.65%</t>
+          <t>'-4.74%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.03</v>
+        <v>1.19</v>
       </c>
       <c r="E16" t="n">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>301</v>
+        <v>120</v>
       </c>
       <c r="H16" t="n">
-        <v>3.09</v>
+        <v>4.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7820</v>
+        <v>4430</v>
       </c>
       <c r="K16" t="n">
-        <v>8080</v>
+        <v>4650</v>
       </c>
       <c r="L16" t="n">
-        <v>8510</v>
+        <v>4855</v>
       </c>
       <c r="M16" t="n">
-        <v>7170</v>
+        <v>4215</v>
       </c>
       <c r="N16" t="n">
-        <v>5.12</v>
+        <v>3.27</v>
       </c>
       <c r="O16" t="n">
-        <v>70242471165</v>
+        <v>60957604353</v>
       </c>
       <c r="P16" t="n">
-        <v>23500</v>
+        <v>5470</v>
       </c>
       <c r="Q16" t="n">
-        <v>2890</v>
+        <v>2810</v>
       </c>
       <c r="R16" t="n">
-        <v>-496000</v>
+        <v>-470000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>건설 및 부동산 관련 내용과 함께 일부 투자자 간의 논쟁이 나타나지만, 종목의 명확한 팩트나 전망에 대한 분석은 부족함.</t>
+          <t>미국 항생제 보유 회사 주가 급등 및 WHO의 러시아 폐렴 관련 언급으로 인한 약품 수요 기대감 형성. 그러나 구체적인 호재는 부족.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['부동산', '건설', '투자자 논쟁']</t>
+          <t>['항생제', '폐렴', 'WHO']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15500</v>
+        <v>17080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.24%</t>
+          <t>'-4.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.44</v>
+        <v>-0.95</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G17" t="n">
-        <v>145</v>
+        <v>299</v>
       </c>
       <c r="H17" t="n">
-        <v>0.93</v>
+        <v>3.97</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>16710</v>
+        <v>17940</v>
       </c>
       <c r="K17" t="n">
-        <v>16460</v>
+        <v>17770</v>
       </c>
       <c r="L17" t="n">
-        <v>17180</v>
+        <v>17940</v>
       </c>
       <c r="M17" t="n">
-        <v>14820</v>
+        <v>16900</v>
       </c>
       <c r="N17" t="n">
-        <v>2.37</v>
+        <v>4.92</v>
       </c>
       <c r="O17" t="n">
-        <v>27086062725</v>
+        <v>58582232165</v>
       </c>
       <c r="P17" t="n">
-        <v>17590</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>6320</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>37000</v>
+        <v>15000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 사이버보안 협의체 선정 및 금융권 해킹 방어 성공 사례, 계약 체결 기대감.</t>
+          <t>미국 광통신주 하락 영향 및 외인 매도세 속 주가 부진. 일부 투자자는 손절 또는 추가 매수 고려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI', '사이버보안', '계약']</t>
+          <t>['광통신', '외인', '매물대']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9860</v>
+        <v>7430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-10.45%</t>
+          <t>'-4.99%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.03</v>
+        <v>-2.03</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G18" t="n">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="H18" t="n">
-        <v>5.04</v>
+        <v>3.09</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>11010</v>
+        <v>7820</v>
       </c>
       <c r="K18" t="n">
-        <v>10110</v>
+        <v>8080</v>
       </c>
       <c r="L18" t="n">
-        <v>10130</v>
+        <v>8510</v>
       </c>
       <c r="M18" t="n">
-        <v>9850</v>
+        <v>7170</v>
       </c>
       <c r="N18" t="n">
-        <v>5.01</v>
+        <v>5.12</v>
       </c>
       <c r="O18" t="n">
-        <v>4533609565</v>
+        <v>73238661785</v>
       </c>
       <c r="P18" t="n">
-        <v>15900</v>
+        <v>23500</v>
       </c>
       <c r="Q18" t="n">
-        <v>6310</v>
+        <v>2890</v>
       </c>
       <c r="R18" t="n">
-        <v>-285000</v>
+        <v>-496000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 항생제 관련 상승세 및 케냐 에볼라 발생 관련 언급, 주가 변동성에 대한 기대감.</t>
+          <t>건설 프로젝트 진행 상황에 대한 정보가 일부 공유되나, 주가 부양 동력 부족 및 공매도 관련 이슈로 인한 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['항생제', '에볼라', '주가']</t>
+          <t>['본PF', '공매', '물량']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2119,6 +2119,374 @@
         </is>
       </c>
       <c r="Z18" t="inlineStr">
+        <is>
+          <t>038500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4930</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-5.37%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>87</v>
+      </c>
+      <c r="F19" t="n">
+        <v>51</v>
+      </c>
+      <c r="G19" t="n">
+        <v>234</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>5210</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5220</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5310</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4755</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="O19" t="n">
+        <v>49724039023</v>
+      </c>
+      <c r="P19" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>592</v>
+      </c>
+      <c r="R19" t="n">
+        <v>237000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>CB 물량 부담 및 기타 법인 매도 공시로 인한 단기적인 주가 하락 우려. 그러나 광통신 산업 성장 가능성에 대한 기대감도 존재.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['CB', '악재', '광통신']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>한미사이언스</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>54400</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'-6.37%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E20" t="n">
+        <v>234</v>
+      </c>
+      <c r="F20" t="n">
+        <v>120</v>
+      </c>
+      <c r="G20" t="n">
+        <v>389</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>58100</v>
+      </c>
+      <c r="K20" t="n">
+        <v>63200</v>
+      </c>
+      <c r="L20" t="n">
+        <v>63800</v>
+      </c>
+      <c r="M20" t="n">
+        <v>53400</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>42012504100</v>
+      </c>
+      <c r="P20" t="n">
+        <v>63800</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>25600</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-154000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>미국 비만주 급등에도 국내 시장은 부진. 불법 조작 거래 의혹 제기 및 신고 움직임.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['비만주', '불법 거래', '국내 시장']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>008930</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>라온시큐어</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>15410</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>'-7.78%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="E21" t="n">
+        <v>48</v>
+      </c>
+      <c r="F21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G21" t="n">
+        <v>146</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>16710</v>
+      </c>
+      <c r="K21" t="n">
+        <v>16460</v>
+      </c>
+      <c r="L21" t="n">
+        <v>17180</v>
+      </c>
+      <c r="M21" t="n">
+        <v>14820</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O21" t="n">
+        <v>27544062390</v>
+      </c>
+      <c r="P21" t="n">
+        <v>17590</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6320</v>
+      </c>
+      <c r="R21" t="n">
+        <v>37000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>KBS 보도 통한 양자보안 기술력 부각 및 AI 사이버보안 협의체 선정. SKT와의 협력 강화 기대감.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['양자보안', 'AI', 'SKT']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>신풍제약</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>9780</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'-11.17%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E22" t="n">
+        <v>72</v>
+      </c>
+      <c r="F22" t="n">
+        <v>51</v>
+      </c>
+      <c r="G22" t="n">
+        <v>291</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>11010</v>
+      </c>
+      <c r="K22" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L22" t="n">
+        <v>10130</v>
+      </c>
+      <c r="M22" t="n">
+        <v>9750</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O22" t="n">
+        <v>5224925050</v>
+      </c>
+      <c r="P22" t="n">
+        <v>15900</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6310</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-285000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>미국 항생제 보유 회사 주가 급등 속 신풍제약은 하락. 공포 세일 중이며 일부 투자자는 1년 뒤 전망.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['항생제', '공포 세일', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>019170</t>
         </is>

--- a/data/trending_integrated_20261008_10.xlsx
+++ b/data/trending_integrated_20261008_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>29901402750</v>
+        <v>30285612340</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB바이오스텝의 바이오 섹터 대장주 역할 기대감 및 에볼라, 페스트 창궐, 간암 FDA 승인 임박 등 다수의 호재성 뉴스에 따른 강한 상승세 전망.</t>
+          <t>HLB바이오스텝의 급등세 및 바이오 섹터 전반의 움직임. 간암 FDA 승인 임박 및 에볼라, 페스트 창궐 관련 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['바이오', '대장주', 'FDA']</t>
+          <t>['급등', '바이오 섹터', 'FDA 승인']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14470</v>
+        <v>14490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.68%</t>
+          <t>'+20.85%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
         <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
         <v>4.43</v>
@@ -702,7 +702,7 @@
         <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>30544117960</v>
+        <v>33109208460</v>
       </c>
       <c r="P3" t="n">
         <v>14980</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성전기향 차세대 유리기판 핵심 글라스 본더 공급 계약 체결. 동종업체 대비 낮은 시가총액으로 높은 상승 기대감.</t>
+          <t>삼성전기향 차세대 유리기판 핵심 글라스 본더 공급 계약 체결. 높은 매출 및 영업이익 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유리기판', '글라스 본더', '공급 계약']</t>
+          <t>['유리기판', '글라스본더', '삼성전기']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11310</v>
+        <v>11330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.47%</t>
+          <t>'+14.68%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H4" t="n">
         <v>37.45</v>
@@ -794,7 +794,7 @@
         <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>41898059605</v>
+        <v>43150925600</v>
       </c>
       <c r="P4" t="n">
         <v>19150</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>피노의 전구체 독점 사업권 및 매출 성장 가능성에 기반한 주가 상승 기대감. 2차전지 섹터 전반의 강세와 ETF 편입 가능성도 긍정적 요인.</t>
+          <t>피노의 전구체 독점 및 양극재 사업 이관. 매출 증가와 차트상 긍정적 흐름에 따른 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['전구체', '매출', '2차전지']</t>
+          <t>['전구체 독점', '양극재', '매출 증가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39250</v>
+        <v>39300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.43%</t>
+          <t>'+8.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H5" t="n">
         <v>31.86</v>
@@ -886,7 +886,7 @@
         <v>31.78</v>
       </c>
       <c r="O5" t="n">
-        <v>81650505600</v>
+        <v>86247307500</v>
       </c>
       <c r="P5" t="n">
         <v>45000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>하락장 속에서 주가 방어 성공 및 추세 전환 기대감. 외국인 순매수 및 4만원 안착 여부가 관건.</t>
+          <t>추세적인 상승 흐름 속 외국인 순매수 유입. 4만원 안착 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['추세', '외국인', '안착']</t>
+          <t>['추세', '외국인', '호가창']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6880</v>
+        <v>6970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.50%</t>
+          <t>'+7.89%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0.31</v>
       </c>
       <c r="O6" t="n">
-        <v>17966953425</v>
+        <v>18223848065</v>
       </c>
       <c r="P6" t="n">
         <v>9680</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>새 주인 확정 및 관리종목 해제 호재에도 주가 하락 지속. 매물대 저항 및 거래량 부족이 발목.</t>
+          <t>관리종목 해제 및 신규 주인 확정 기대감. 주가 하락 및 적정가 논란.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['관리종목', '신규 주인', '거래량']</t>
+          <t>['관리종목해제', '신규인수', '적정가']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13170</v>
+        <v>12910</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.77%</t>
+          <t>'+2.70%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H7" t="n">
         <v>1.07</v>
@@ -1070,7 +1070,7 @@
         <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>40140600220</v>
+        <v>43199971160</v>
       </c>
       <c r="P7" t="n">
         <v>22250</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유증 물량 정리 후 주가 반등 기대감. 비만 치료제 개발 이슈와 HLB 승인 여부가 주요 관전 포인트.</t>
+          <t>유증 물량 정리 및 13,500원 돌파 기대감. 비만 치료제 개발 소식.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유증', '비만치료제', 'HLB']</t>
+          <t>['유증', '비만치료제', '매물대']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1743000</v>
+        <v>1750000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.16%</t>
+          <t>'+1.57%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G8" t="n">
-        <v>2013</v>
+        <v>1855</v>
       </c>
       <c r="H8" t="n">
         <v>49.59</v>
@@ -1153,7 +1153,7 @@
         <v>1722000</v>
       </c>
       <c r="L8" t="n">
-        <v>1750000</v>
+        <v>1751000</v>
       </c>
       <c r="M8" t="n">
         <v>1722000</v>
@@ -1162,7 +1162,7 @@
         <v>49.71</v>
       </c>
       <c r="O8" t="n">
-        <v>1486042575000</v>
+        <v>1578698825000</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>마이크론의 급등 및 2028년까지 반도체 부족 현상 전망에 따른 SK하이닉스의 상승 기대감.</t>
+          <t>마이크론 급등에 따른 반등 기대감. 솔리다임 관련 주주 가치 훼손 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['마이크론', '반도체 부족', '상승 기대']</t>
+          <t>['마이크론', '반등', '솔리다임']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8300</v>
+        <v>8310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.61%</t>
+          <t>'+0.73%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H9" t="n">
         <v>26.38</v>
@@ -1254,7 +1254,7 @@
         <v>26.55</v>
       </c>
       <c r="O9" t="n">
-        <v>8040823110</v>
+        <v>8315949575</v>
       </c>
       <c r="P9" t="n">
         <v>17950</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>나스닥 ADR 폭락 및 회사의 고질적인 적자 문제로 인한 투자 심리 악화. 경영 능력에 대한 비판과 주가 하락 전망이 지배적.</t>
+          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['적자', '경영', '공매도']</t>
+          <t>['주가 하락', '경영 부실', '적자']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45850</v>
+        <v>267750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.11%</t>
+          <t>'-0.28%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.73</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>147</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>88</v>
+        <v>560</v>
       </c>
       <c r="G10" t="n">
-        <v>495</v>
+        <v>2005</v>
       </c>
       <c r="H10" t="n">
-        <v>13.39</v>
+        <v>46.38</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>45900</v>
+        <v>268500</v>
       </c>
       <c r="K10" t="n">
-        <v>45950</v>
+        <v>269500</v>
       </c>
       <c r="L10" t="n">
-        <v>46500</v>
+        <v>270000</v>
       </c>
       <c r="M10" t="n">
-        <v>45100</v>
+        <v>266000</v>
       </c>
       <c r="N10" t="n">
-        <v>14.12</v>
+        <v>46.37</v>
       </c>
       <c r="O10" t="n">
-        <v>15484529300</v>
+        <v>1395414453250</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>90200</v>
       </c>
       <c r="R10" t="n">
-        <v>-14000</v>
+        <v>-246000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-228000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>글로벌 3상 임상 종료 약물에 대한 기대감과 공매도 압박 속 우상향 추세 전망.</t>
+          <t>삼성전자의 3분기 108조 수익에도 불구하고 주가 하락 지속. 정치적 요인 및 외국인, 기관의 움직임에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '임상', '우상향']</t>
+          <t>['영업이익', '주가 하락', '정치적 요인']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>267750</v>
+        <v>45500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.28%</t>
+          <t>'-0.87%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>-0.73</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>156</v>
       </c>
       <c r="F11" t="n">
-        <v>563</v>
+        <v>95</v>
       </c>
       <c r="G11" t="n">
-        <v>2077</v>
+        <v>521</v>
       </c>
       <c r="H11" t="n">
-        <v>46.38</v>
+        <v>13.39</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>268500</v>
+        <v>45900</v>
       </c>
       <c r="K11" t="n">
-        <v>269500</v>
+        <v>45950</v>
       </c>
       <c r="L11" t="n">
-        <v>270000</v>
+        <v>46500</v>
       </c>
       <c r="M11" t="n">
-        <v>266000</v>
+        <v>45100</v>
       </c>
       <c r="N11" t="n">
-        <v>46.37</v>
+        <v>14.12</v>
       </c>
       <c r="O11" t="n">
-        <v>1333740295750</v>
+        <v>16472398700</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>90200</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>-246000</v>
+        <v>-14000</v>
       </c>
       <c r="S11" t="n">
-        <v>-228000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>역대급 3분기 영업이익에도 불구하고 주가 하락이 지속되는 상황에 대한 불만과 정치적 책임론 제기.</t>
+          <t>리보세라닙 병용요법 허가 기대감 속 공매도 압력. 우상향 차트 지속.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['영업이익', '주가하락', '국장']</t>
+          <t>['리보세라닙', '공매도', '우상향']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19100</v>
+        <v>19085</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.25%</t>
+          <t>'-2.33%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H12" t="n">
         <v>27.68</v>
@@ -1530,7 +1530,7 @@
         <v>27.67</v>
       </c>
       <c r="O12" t="n">
-        <v>18976481340</v>
+        <v>19790656905</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>글로벌 조선업 경쟁 심화 및 수주 부진 가능성에 대한 우려로 주가 하락세 지속. 애널리스트에 대한 불신과 투자 전략 부재 지적.</t>
+          <t>삼성중공업의 5개월간 주가 하락세 지속 및 52주 신저점 근접. 애널리스트 불신 및 조선업계 수주 경쟁 심화.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선업', '수주', '신저점']</t>
+          <t>['주가 하락', '52주 신저점', '조선업']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16830</v>
+        <v>16810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.94%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="H13" t="n">
         <v>9.460000000000001</v>
@@ -1622,7 +1622,7 @@
         <v>9.5</v>
       </c>
       <c r="O13" t="n">
-        <v>20631655150</v>
+        <v>21340524530</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 및 대차 해지에 대한 관심이 높으나, 실질적인 주가 부양 근거나 명확한 호재는 부족한 상황.</t>
+          <t>공매도 및 대차 거래에 대한 우려와 주가 하락에 대한 불만. 주주들의 호소와 행동 촉구.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '연기금']</t>
+          <t>['공매도', '대차 거래', '주주 호소']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>232500</v>
+        <v>233000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-3.32%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.65</v>
       </c>
       <c r="E14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14" t="n">
-        <v>490</v>
+        <v>516</v>
       </c>
       <c r="H14" t="n">
         <v>3.47</v>
@@ -1714,7 +1714,7 @@
         <v>4.12</v>
       </c>
       <c r="O14" t="n">
-        <v>26686605500</v>
+        <v>27455086000</v>
       </c>
       <c r="P14" t="n">
         <v>1233000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 과열 종목 지정 속 연기금 7일 연속 순매수. 캐나다 세마 출시 및 릴레이 계약 공시 기대감.</t>
+          <t>공매도 금지 조치 속 릴레이 계약 공시 기대감. 연기금 순매수 지속.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '연기금', '계약 공시']</t>
+          <t>['공매도금지', '계약공시', '연기금']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>76700</v>
+        <v>28700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.72%</t>
+          <t>'-3.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.1</v>
+        <v>-0.76</v>
       </c>
       <c r="E15" t="n">
-        <v>196</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>536</v>
+        <v>99</v>
       </c>
       <c r="H15" t="n">
-        <v>22.49</v>
+        <v>10.02</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,47 +1791,47 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>80500</v>
+        <v>29800</v>
       </c>
       <c r="K15" t="n">
-        <v>79600</v>
+        <v>29900</v>
       </c>
       <c r="L15" t="n">
-        <v>79600</v>
+        <v>30000</v>
       </c>
       <c r="M15" t="n">
-        <v>76500</v>
+        <v>28400</v>
       </c>
       <c r="N15" t="n">
-        <v>22.59</v>
+        <v>10.78</v>
       </c>
       <c r="O15" t="n">
-        <v>91434592150</v>
+        <v>35457229875</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>75900</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>15960</v>
       </c>
       <c r="R15" t="n">
-        <v>-83000</v>
+        <v>-254000</v>
       </c>
       <c r="S15" t="n">
-        <v>-40000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 원전주 하락 영향과 더불어 국내 원전 관련 사업 진행 불확실성으로 인한 하락세 지속. 구체적인 수출 호재 언급은 있으나 투자 심리 위축.</t>
+          <t>대한전선의 급락 및 계단식 하락 추세. 회사의 주주 노력 부족과 외국인 매도세에 대한 불만.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '수출', '하락']</t>
+          <t>['주가 하락', '외국인 매도', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4220</v>
+        <v>17110</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.74%</t>
+          <t>'-4.63%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.19</v>
+        <v>-0.95</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>120</v>
+        <v>303</v>
       </c>
       <c r="H16" t="n">
-        <v>4.46</v>
+        <v>3.97</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4430</v>
+        <v>17940</v>
       </c>
       <c r="K16" t="n">
-        <v>4650</v>
+        <v>17770</v>
       </c>
       <c r="L16" t="n">
-        <v>4855</v>
+        <v>17940</v>
       </c>
       <c r="M16" t="n">
-        <v>4215</v>
+        <v>16900</v>
       </c>
       <c r="N16" t="n">
-        <v>3.27</v>
+        <v>4.92</v>
       </c>
       <c r="O16" t="n">
-        <v>60957604353</v>
+        <v>60133813285</v>
       </c>
       <c r="P16" t="n">
-        <v>5470</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>2810</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-470000</v>
+        <v>15000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 급등 및 WHO의 러시아 폐렴 관련 언급으로 인한 약품 수요 기대감 형성. 그러나 구체적인 호재는 부족.</t>
+          <t>미국 광통신주 하락 영향 및 외인 매도세 속 주가 부진. 일부 투자자는 손절 또는 추가 매수 고려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['항생제', '폐렴', 'WHO']</t>
+          <t>['광통신', '외인', '매물대']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17080</v>
+        <v>76600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.79%</t>
+          <t>'-4.84%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.95</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="G17" t="n">
-        <v>299</v>
+        <v>607</v>
       </c>
       <c r="H17" t="n">
-        <v>3.97</v>
+        <v>22.49</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17940</v>
+        <v>80500</v>
       </c>
       <c r="K17" t="n">
-        <v>17770</v>
+        <v>79600</v>
       </c>
       <c r="L17" t="n">
-        <v>17940</v>
+        <v>79600</v>
       </c>
       <c r="M17" t="n">
-        <v>16900</v>
+        <v>76400</v>
       </c>
       <c r="N17" t="n">
-        <v>4.92</v>
+        <v>22.59</v>
       </c>
       <c r="O17" t="n">
-        <v>58582232165</v>
+        <v>103405253900</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>15000</v>
+        <v>-83000</v>
       </c>
       <c r="S17" t="n">
-        <v>-8000</v>
+        <v>-40000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락 영향 및 외인 매도세 속 주가 부진. 일부 투자자는 손절 또는 추가 매수 고려.</t>
+          <t>미국 텍사스 가스 발전 수주에도 불구하고 주가 하락세. 연말 수익률 평가 및 외국인 매도세에 대한 불안감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '외인', '매물대']</t>
+          <t>['수주', '주가 하락', '외국인 매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7430</v>
+        <v>4955</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.99%</t>
+          <t>'-4.89%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-2.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F18" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>324</v>
+        <v>243</v>
       </c>
       <c r="H18" t="n">
-        <v>3.09</v>
+        <v>4.65</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7820</v>
+        <v>5210</v>
       </c>
       <c r="K18" t="n">
-        <v>8080</v>
+        <v>5220</v>
       </c>
       <c r="L18" t="n">
-        <v>8510</v>
+        <v>5310</v>
       </c>
       <c r="M18" t="n">
-        <v>7170</v>
+        <v>4755</v>
       </c>
       <c r="N18" t="n">
-        <v>5.12</v>
+        <v>4.72</v>
       </c>
       <c r="O18" t="n">
-        <v>73238661785</v>
+        <v>52416537537</v>
       </c>
       <c r="P18" t="n">
-        <v>23500</v>
+        <v>8100</v>
       </c>
       <c r="Q18" t="n">
-        <v>2890</v>
+        <v>592</v>
       </c>
       <c r="R18" t="n">
-        <v>-496000</v>
+        <v>237000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>건설 프로젝트 진행 상황에 대한 정보가 일부 공유되나, 주가 부양 동력 부족 및 공매도 관련 이슈로 인한 투자 심리 위축.</t>
+          <t>빛과전자의 CB 발행 및 기타법인 매도에 따른 주가 하락 우려. 장기 전망에 대한 긍정적 언급도 존재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['본PF', '공매', '물량']</t>
+          <t>['CB 발행', '장내매도', '광통신']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4930</v>
+        <v>4210</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.37%</t>
+          <t>'-4.97%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="E19" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G19" t="n">
-        <v>234</v>
+        <v>120</v>
       </c>
       <c r="H19" t="n">
-        <v>4.65</v>
+        <v>4.46</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5210</v>
+        <v>4430</v>
       </c>
       <c r="K19" t="n">
-        <v>5220</v>
+        <v>4650</v>
       </c>
       <c r="L19" t="n">
-        <v>5310</v>
+        <v>4855</v>
       </c>
       <c r="M19" t="n">
-        <v>4755</v>
+        <v>4185</v>
       </c>
       <c r="N19" t="n">
-        <v>4.72</v>
+        <v>3.27</v>
       </c>
       <c r="O19" t="n">
-        <v>49724039023</v>
+        <v>61951193615</v>
       </c>
       <c r="P19" t="n">
-        <v>8100</v>
+        <v>5470</v>
       </c>
       <c r="Q19" t="n">
-        <v>592</v>
+        <v>2810</v>
       </c>
       <c r="R19" t="n">
-        <v>237000</v>
+        <v>-470000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>CB 물량 부담 및 기타 법인 매도 공시로 인한 단기적인 주가 하락 우려. 그러나 광통신 산업 성장 가능성에 대한 기대감도 존재.</t>
+          <t>미국 항생제 보유 회사 주가 급등 및 WHO의 러시아 폐렴 관련 언급으로 인한 약품 수요 기대감 형성. 그러나 구체적인 호재는 부족.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['CB', '악재', '광통신']</t>
+          <t>['항생제', '폐렴', 'WHO']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>54400</v>
+        <v>7360</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.37%</t>
+          <t>'-5.88%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.02</v>
+        <v>-2.03</v>
       </c>
       <c r="E20" t="n">
-        <v>234</v>
+        <v>119</v>
       </c>
       <c r="F20" t="n">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="G20" t="n">
-        <v>389</v>
+        <v>336</v>
       </c>
       <c r="H20" t="n">
-        <v>1.32</v>
+        <v>3.09</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>58100</v>
+        <v>7820</v>
       </c>
       <c r="K20" t="n">
-        <v>63200</v>
+        <v>8080</v>
       </c>
       <c r="L20" t="n">
-        <v>63800</v>
+        <v>8510</v>
       </c>
       <c r="M20" t="n">
-        <v>53400</v>
+        <v>7170</v>
       </c>
       <c r="N20" t="n">
-        <v>1.3</v>
+        <v>5.12</v>
       </c>
       <c r="O20" t="n">
-        <v>42012504100</v>
+        <v>74444465840</v>
       </c>
       <c r="P20" t="n">
-        <v>63800</v>
+        <v>23500</v>
       </c>
       <c r="Q20" t="n">
-        <v>25600</v>
+        <v>2890</v>
       </c>
       <c r="R20" t="n">
-        <v>-154000</v>
+        <v>-496000</v>
       </c>
       <c r="S20" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 비만주 급등에도 국내 시장은 부진. 불법 조작 거래 의혹 제기 및 신고 움직임.</t>
+          <t>삼표시멘트의 주가 하락세와 공매도에 대한 불만. 부동산 PF 및 건설 관련 이슈 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['비만주', '불법 거래', '국내 시장']</t>
+          <t>['주가 하락', '공매도', '부동산 PF']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,90 +2304,90 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15410</v>
+        <v>54300</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.78%</t>
+          <t>'-6.54%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.44</v>
+        <v>0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>48</v>
+        <v>237</v>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="G21" t="n">
-        <v>146</v>
+        <v>420</v>
       </c>
       <c r="H21" t="n">
-        <v>0.93</v>
+        <v>1.32</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>16710</v>
+        <v>58100</v>
       </c>
       <c r="K21" t="n">
-        <v>16460</v>
+        <v>63200</v>
       </c>
       <c r="L21" t="n">
-        <v>17180</v>
+        <v>63800</v>
       </c>
       <c r="M21" t="n">
-        <v>14820</v>
+        <v>53400</v>
       </c>
       <c r="N21" t="n">
-        <v>2.37</v>
+        <v>1.3</v>
       </c>
       <c r="O21" t="n">
-        <v>27544062390</v>
+        <v>42531111500</v>
       </c>
       <c r="P21" t="n">
-        <v>17590</v>
+        <v>63800</v>
       </c>
       <c r="Q21" t="n">
-        <v>6320</v>
+        <v>25600</v>
       </c>
       <c r="R21" t="n">
-        <v>37000</v>
+        <v>-154000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>KBS 보도 통한 양자보안 기술력 부각 및 AI 사이버보안 협의체 선정. SKT와의 협력 강화 기대감.</t>
+          <t>국내 비만약 개발 기대감 속 주가조작 신고 및 급락 우려. 한미약품과의 관계 논란.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['양자보안', 'AI', 'SKT']</t>
+          <t>['비만약', '주가조작', '급락']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,86 +2396,86 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9780</v>
+        <v>15360</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-11.17%</t>
+          <t>'-8.08%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.03</v>
+        <v>-1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F22" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="G22" t="n">
-        <v>291</v>
+        <v>149</v>
       </c>
       <c r="H22" t="n">
-        <v>5.04</v>
+        <v>0.93</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>11010</v>
+        <v>16710</v>
       </c>
       <c r="K22" t="n">
-        <v>10110</v>
+        <v>16460</v>
       </c>
       <c r="L22" t="n">
-        <v>10130</v>
+        <v>17180</v>
       </c>
       <c r="M22" t="n">
-        <v>9750</v>
+        <v>14820</v>
       </c>
       <c r="N22" t="n">
-        <v>5.01</v>
+        <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>5224925050</v>
+        <v>27870400510</v>
       </c>
       <c r="P22" t="n">
-        <v>15900</v>
+        <v>17590</v>
       </c>
       <c r="Q22" t="n">
-        <v>6310</v>
+        <v>6320</v>
       </c>
       <c r="R22" t="n">
-        <v>-285000</v>
+        <v>37000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 급등 속 신풍제약은 하락. 공포 세일 중이며 일부 투자자는 1년 뒤 전망.</t>
+          <t>양자보안 기술 KDB생명 해킹 방어 성공. AI 사이버보안 협의체 선정. 고가 놀이 및 매수세 관찰.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['항생제', '공포 세일', '주가 하락']</t>
+          <t>['양자보안', 'AI', '사이버보안']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2487,6 +2487,98 @@
         </is>
       </c>
       <c r="Z22" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>신풍제약</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>9800</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>'-10.99%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E23" t="n">
+        <v>75</v>
+      </c>
+      <c r="F23" t="n">
+        <v>52</v>
+      </c>
+      <c r="G23" t="n">
+        <v>297</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>11010</v>
+      </c>
+      <c r="K23" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10130</v>
+      </c>
+      <c r="M23" t="n">
+        <v>9750</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O23" t="n">
+        <v>5376194290</v>
+      </c>
+      <c r="P23" t="n">
+        <v>15900</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6310</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-285000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>미국 항생제 보유 회사 주가 급등 속 신풍제약은 하락. 공포 세일 중이며 일부 투자자는 1년 뒤 전망.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['항생제', '공포 세일', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>019170</t>
         </is>

--- a/data/trending_integrated_20261008_10.xlsx
+++ b/data/trending_integrated_20261008_10.xlsx
@@ -584,7 +584,7 @@
         <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30285612340</v>
+        <v>30381234080</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB바이오스텝의 급등세 및 바이오 섹터 전반의 움직임. 간암 FDA 승인 임박 및 에볼라, 페스트 창궐 관련 기대감.</t>
+          <t>에볼라, 페스트 창궐 및 간암 FDA 승인 임박 관련 바이오 섹터 동반 강세. HLB바이오스텝이 섹터 대장주로 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['급등', '바이오 섹터', 'FDA 승인']</t>
+          <t>['바이오 섹터', 'FDA 승인', '간암']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14490</v>
+        <v>14340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.85%</t>
+          <t>'+19.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H3" t="n">
         <v>4.43</v>
@@ -702,7 +702,7 @@
         <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>33109208460</v>
+        <v>34214211370</v>
       </c>
       <c r="P3" t="n">
         <v>14980</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성전기향 차세대 유리기판 핵심 글라스 본더 공급 계약 체결. 높은 매출 및 영업이익 전망.</t>
+          <t>삼성전기향 차세대 유리기판 핵심 부품 공급 계약 및 공동 개발 뉴스 기반 강세. 매출 및 영업이익 증가 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유리기판', '글라스본더', '삼성전기']</t>
+          <t>['유리기판', '글라스본더', '공급']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11330</v>
+        <v>11270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.68%</t>
+          <t>'+14.07%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H4" t="n">
         <v>37.45</v>
@@ -794,7 +794,7 @@
         <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>43150925600</v>
+        <v>44849951115</v>
       </c>
       <c r="P4" t="n">
         <v>19150</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>피노의 전구체 독점 및 양극재 사업 이관. 매출 증가와 차트상 긍정적 흐름에 따른 기대감.</t>
+          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['전구체 독점', '양극재', '매출 증가']</t>
+          <t>['전구체', '양극재', '매출']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39300</v>
+        <v>39000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.56%</t>
+          <t>'+7.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="H5" t="n">
         <v>31.86</v>
@@ -886,7 +886,7 @@
         <v>31.78</v>
       </c>
       <c r="O5" t="n">
-        <v>86247307500</v>
+        <v>90959085800</v>
       </c>
       <c r="P5" t="n">
         <v>45000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>추세적인 상승 흐름 속 외국인 순매수 유입. 4만원 안착 기대감.</t>
+          <t>하락장 속에서 주가 방어 및 기관/외국인 매수세 유입. 4만원 안착 시 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['추세', '외국인', '호가창']</t>
+          <t>['기관', '외국인', '매수세']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6970</v>
+        <v>6790</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.89%</t>
+          <t>'+5.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0.31</v>
       </c>
       <c r="O6" t="n">
-        <v>18223848065</v>
+        <v>18661427740</v>
       </c>
       <c r="P6" t="n">
         <v>9680</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>관리종목 해제 및 신규 주인 확정 기대감. 주가 하락 및 적정가 논란.</t>
+          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['관리종목해제', '신규인수', '적정가']</t>
+          <t>['관리종목', '해제', '호재']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12910</v>
+        <v>13070</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.70%</t>
+          <t>'+3.98%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H7" t="n">
         <v>1.07</v>
@@ -1070,7 +1070,7 @@
         <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>43199971160</v>
+        <v>45830695075</v>
       </c>
       <c r="P7" t="n">
         <v>22250</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유증 물량 정리 및 13,500원 돌파 기대감. 비만 치료제 개발 소식.</t>
+          <t>유증 물량 소화 완료 및 비만치료제 개발 기대감. HLB 그룹주 동반 상승 가능성과 함께 목표 주가 3만원 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유증', '비만치료제', '매물대']</t>
+          <t>['유상증자', '비만치료제', 'HLB 그룹주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1750000</v>
+        <v>1756000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.57%</t>
+          <t>'+1.92%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="G8" t="n">
-        <v>1855</v>
+        <v>1782</v>
       </c>
       <c r="H8" t="n">
         <v>49.59</v>
@@ -1153,7 +1153,7 @@
         <v>1722000</v>
       </c>
       <c r="L8" t="n">
-        <v>1751000</v>
+        <v>1758000</v>
       </c>
       <c r="M8" t="n">
         <v>1722000</v>
@@ -1162,7 +1162,7 @@
         <v>49.71</v>
       </c>
       <c r="O8" t="n">
-        <v>1578698825000</v>
+        <v>1707568061500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>마이크론 급등에 따른 반등 기대감. 솔리다임 관련 주주 가치 훼손 우려.</t>
+          <t>마이크론 주가 급등 및 2028년까지 반도체 부족 전망 뉴스. 일부 솔리다임 관련 악재에도 불구하고 반등 기대감 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['마이크론', '반등', '솔리다임']</t>
+          <t>['마이크론', '반도체 부족', 'ADR']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,18 +1211,18 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8310</v>
+        <v>8260</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.73%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>34</v>
@@ -1254,7 +1254,7 @@
         <v>26.55</v>
       </c>
       <c r="O9" t="n">
-        <v>8315949575</v>
+        <v>9035642290</v>
       </c>
       <c r="P9" t="n">
         <v>17950</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>267750</v>
+        <v>268500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.28%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="G10" t="n">
-        <v>2005</v>
+        <v>2075</v>
       </c>
       <c r="H10" t="n">
         <v>46.38</v>
@@ -1346,7 +1346,7 @@
         <v>46.37</v>
       </c>
       <c r="O10" t="n">
-        <v>1395414453250</v>
+        <v>1531907314250</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성전자의 3분기 108조 수익에도 불구하고 주가 하락 지속. 정치적 요인 및 외국인, 기관의 움직임에 대한 불만 제기.</t>
+          <t>사상 최대 분기 영업이익(108조)에도 불구하고 주가 하락 지속. 정치적 요인 및 외국인/기관의 매도세에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '정치적 요인']</t>
+          <t>['영업이익', '주가 하락', '외국인 매매']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45500</v>
+        <v>45550</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.87%</t>
+          <t>'-0.76%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.73</v>
       </c>
       <c r="E11" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F11" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="H11" t="n">
         <v>13.39</v>
@@ -1438,7 +1438,7 @@
         <v>14.12</v>
       </c>
       <c r="O11" t="n">
-        <v>16472398700</v>
+        <v>17398299800</v>
       </c>
       <c r="P11" t="n">
         <v>69200</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>리보세라닙 병용요법 허가 기대감 속 공매도 압력. 우상향 차트 지속.</t>
+          <t>공매도 압박 속에서도 우상향 차트 기반 기대감. 리보세라닙 병용요법 허가 가능성 및 3상 종료 약물에 대한 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['리보세라닙', '공매도', '우상향']</t>
+          <t>['공매도', '우상향', '리보세라닙']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19085</v>
+        <v>19080</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.33%</t>
+          <t>'-2.35%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
         <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="H12" t="n">
         <v>27.68</v>
@@ -1530,7 +1530,7 @@
         <v>27.67</v>
       </c>
       <c r="O12" t="n">
-        <v>19790656905</v>
+        <v>21142197990</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성중공업의 5개월간 주가 하락세 지속 및 52주 신저점 근접. 애널리스트 불신 및 조선업계 수주 경쟁 심화.</t>
+          <t>5개월간 주가 하락세 지속 및 52주 신저가 경신 가능성 언급. 증권사 애널리스트에 대한 불신 및 폐업 우려 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가 하락', '52주 신저점', '조선업']</t>
+          <t>['주가 하락', '신저가', '애널리스트']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16810</v>
+        <v>16820</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-3.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="H13" t="n">
         <v>9.460000000000001</v>
@@ -1622,7 +1622,7 @@
         <v>9.5</v>
       </c>
       <c r="O13" t="n">
-        <v>21340524530</v>
+        <v>22635619730</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>233000</v>
+        <v>232500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.32%</t>
+          <t>'-3.53%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>63</v>
       </c>
       <c r="G14" t="n">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="H14" t="n">
         <v>3.47</v>
@@ -1714,7 +1714,7 @@
         <v>4.12</v>
       </c>
       <c r="O14" t="n">
-        <v>27455086000</v>
+        <v>28603048000</v>
       </c>
       <c r="P14" t="n">
         <v>1233000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 금지 조치 속 릴레이 계약 공시 기대감. 연기금 순매수 지속.</t>
+          <t>공매도 금지 조치 속 릴레이 계약 공시 기대감. 연기금 7일째 매수세 유입 및 바이오 섹터 내 경쟁력 부각.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도금지', '계약공시', '연기금']</t>
+          <t>['공매도', '계약공시', '연기금']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28700</v>
+        <v>28650</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.69%</t>
+          <t>'-3.86%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.76</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
         <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H15" t="n">
         <v>10.02</v>
@@ -1806,7 +1806,7 @@
         <v>10.78</v>
       </c>
       <c r="O15" t="n">
-        <v>35457229875</v>
+        <v>36619153825</v>
       </c>
       <c r="P15" t="n">
         <v>75900</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대한전선의 급락 및 계단식 하락 추세. 회사의 주주 노력 부족과 외국인 매도세에 대한 불만.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 하락', '외국인 매도', '공매도']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17110</v>
+        <v>4245</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.63%</t>
+          <t>'-4.18%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.95</v>
+        <v>1.19</v>
       </c>
       <c r="E16" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>303</v>
+        <v>121</v>
       </c>
       <c r="H16" t="n">
-        <v>3.97</v>
+        <v>4.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17940</v>
+        <v>4430</v>
       </c>
       <c r="K16" t="n">
-        <v>17770</v>
+        <v>4650</v>
       </c>
       <c r="L16" t="n">
-        <v>17940</v>
+        <v>4855</v>
       </c>
       <c r="M16" t="n">
-        <v>16900</v>
+        <v>4185</v>
       </c>
       <c r="N16" t="n">
-        <v>4.92</v>
+        <v>3.27</v>
       </c>
       <c r="O16" t="n">
-        <v>60133813285</v>
+        <v>62736496272</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>5470</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>2810</v>
       </c>
       <c r="R16" t="n">
-        <v>15000</v>
+        <v>-470000</v>
       </c>
       <c r="S16" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락 영향 및 외인 매도세 속 주가 부진. 일부 투자자는 손절 또는 추가 매수 고려.</t>
+          <t>미국 항생제 보유 회사 주가 200% 폭등 및 WHO 페스트 관련 뉴스 속보. 다만, 전염병 확산은 제한적이며, 주가 흐름은 미미함.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '외인', '매물대']</t>
+          <t>['미국 항생제', '페스트', 'WHO']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>76600</v>
+        <v>17130</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.84%</t>
+          <t>'-4.52%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1</v>
+        <v>-0.95</v>
       </c>
       <c r="E17" t="n">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="F17" t="n">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
-        <v>607</v>
+        <v>314</v>
       </c>
       <c r="H17" t="n">
-        <v>22.49</v>
+        <v>3.97</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>80500</v>
+        <v>17940</v>
       </c>
       <c r="K17" t="n">
-        <v>79600</v>
+        <v>17770</v>
       </c>
       <c r="L17" t="n">
-        <v>79600</v>
+        <v>17940</v>
       </c>
       <c r="M17" t="n">
-        <v>76400</v>
+        <v>16900</v>
       </c>
       <c r="N17" t="n">
-        <v>22.59</v>
+        <v>4.92</v>
       </c>
       <c r="O17" t="n">
-        <v>103405253900</v>
+        <v>62557963485</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-83000</v>
+        <v>15000</v>
       </c>
       <c r="S17" t="n">
-        <v>-40000</v>
+        <v>-8000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 텍사스 가스 발전 수주에도 불구하고 주가 하락세. 연말 수익률 평가 및 외국인 매도세에 대한 불안감.</t>
+          <t>미국 광통신 주가 하락세 및 적자 기업이라는 부정적 요인. 외인 매도세와 프로그램 매매에 대한 우려 속에서 주가 하락.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['수주', '주가 하락', '외국인 매도']</t>
+          <t>['광통신', '적자', '외인 매매']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4955</v>
+        <v>76700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.89%</t>
+          <t>'-4.72%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>86</v>
+        <v>225</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="G18" t="n">
-        <v>243</v>
+        <v>638</v>
       </c>
       <c r="H18" t="n">
-        <v>4.65</v>
+        <v>22.49</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>5210</v>
+        <v>80500</v>
       </c>
       <c r="K18" t="n">
-        <v>5220</v>
+        <v>79600</v>
       </c>
       <c r="L18" t="n">
-        <v>5310</v>
+        <v>79600</v>
       </c>
       <c r="M18" t="n">
-        <v>4755</v>
+        <v>76300</v>
       </c>
       <c r="N18" t="n">
-        <v>4.72</v>
+        <v>22.59</v>
       </c>
       <c r="O18" t="n">
-        <v>52416537537</v>
+        <v>111963245850</v>
       </c>
       <c r="P18" t="n">
-        <v>8100</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>592</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>237000</v>
+        <v>-83000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-40000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>빛과전자의 CB 발행 및 기타법인 매도에 따른 주가 하락 우려. 장기 전망에 대한 긍정적 언급도 존재.</t>
+          <t>미국 텍사스 가스 발전 수주에도 불구하고 주가 하락세. 연말 수익률 평가 및 외국인 매도세에 대한 불안감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['CB 발행', '장내매도', '광통신']</t>
+          <t>['수주', '주가 하락', '외국인 매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4210</v>
+        <v>4950</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.97%</t>
+          <t>'-4.99%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.19</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="F19" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
-        <v>120</v>
+        <v>257</v>
       </c>
       <c r="H19" t="n">
-        <v>4.46</v>
+        <v>4.65</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>4430</v>
+        <v>5210</v>
       </c>
       <c r="K19" t="n">
-        <v>4650</v>
+        <v>5220</v>
       </c>
       <c r="L19" t="n">
-        <v>4855</v>
+        <v>5310</v>
       </c>
       <c r="M19" t="n">
-        <v>4185</v>
+        <v>4755</v>
       </c>
       <c r="N19" t="n">
-        <v>3.27</v>
+        <v>4.72</v>
       </c>
       <c r="O19" t="n">
-        <v>61951193615</v>
+        <v>54550088210</v>
       </c>
       <c r="P19" t="n">
-        <v>5470</v>
+        <v>8100</v>
       </c>
       <c r="Q19" t="n">
-        <v>2810</v>
+        <v>592</v>
       </c>
       <c r="R19" t="n">
-        <v>-470000</v>
+        <v>237000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 급등 및 WHO의 러시아 폐렴 관련 언급으로 인한 약품 수요 기대감 형성. 그러나 구체적인 호재는 부족.</t>
+          <t>빛과전자의 CB 발행 및 기타법인 매도에 따른 주가 하락 우려. 장기 전망에 대한 긍정적 언급도 존재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['항생제', '폐렴', 'WHO']</t>
+          <t>['CB 발행', '장내매도', '광통신']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7360</v>
+        <v>7310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.88%</t>
+          <t>'-6.52%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-2.03</v>
       </c>
       <c r="E20" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F20" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G20" t="n">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="H20" t="n">
         <v>3.09</v>
@@ -2266,7 +2266,7 @@
         <v>5.12</v>
       </c>
       <c r="O20" t="n">
-        <v>74444465840</v>
+        <v>75474788400</v>
       </c>
       <c r="P20" t="n">
         <v>23500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>삼표시멘트의 주가 하락세와 공매도에 대한 불만. 부동산 PF 및 건설 관련 이슈 언급.</t>
+          <t>주가 급락 및 공매도에 대한 비판. 성수동 부동산 개발 관련 기대감도 있으나, 전반적으로 부정적 전망 우세.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '부동산 PF']</t>
+          <t>['주가 급락', '공매도', '부동산 개발']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>54300</v>
+        <v>53800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.54%</t>
+          <t>'-7.40%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="F21" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G21" t="n">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="H21" t="n">
         <v>1.32</v>
@@ -2352,13 +2352,13 @@
         <v>63800</v>
       </c>
       <c r="M21" t="n">
-        <v>53400</v>
+        <v>53200</v>
       </c>
       <c r="N21" t="n">
         <v>1.3</v>
       </c>
       <c r="O21" t="n">
-        <v>42531111500</v>
+        <v>43836177800</v>
       </c>
       <c r="P21" t="n">
         <v>63800</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>국내 비만약 개발 기대감 속 주가조작 신고 및 급락 우려. 한미약품과의 관계 논란.</t>
+          <t>국내 최초 비만약 관련 기대감에도 불구하고 주가 급락 및 주가 조작 의혹 제기. 유통 물량 제한적.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15360</v>
+        <v>15320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.08%</t>
+          <t>'-8.32%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F22" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="H22" t="n">
         <v>0.93</v>
@@ -2450,7 +2450,7 @@
         <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>27870400510</v>
+        <v>28665392375</v>
       </c>
       <c r="P22" t="n">
         <v>17590</v>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>양자보안 기술 KDB생명 해킹 방어 성공. AI 사이버보안 협의체 선정. 고가 놀이 및 매수세 관찰.</t>
+          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9800</v>
+        <v>9780</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.99%</t>
+          <t>'-11.17%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.03</v>
       </c>
       <c r="E23" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F23" t="n">
         <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="H23" t="n">
         <v>5.04</v>
@@ -2542,7 +2542,7 @@
         <v>5.01</v>
       </c>
       <c r="O23" t="n">
-        <v>5376194290</v>
+        <v>5490593360</v>
       </c>
       <c r="P23" t="n">
         <v>15900</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 급등 속 신풍제약은 하락. 공포 세일 중이며 일부 투자자는 1년 뒤 전망.</t>
+          <t>미국 항생제 회사 주가 급등 및 케냐 에볼라 확진 소식에 따른 기대감. 그러나 과거 패턴 언급 및 주가 하락 지속.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['항생제', '공포 세일', '주가 하락']</t>
+          <t>['항생제', '에볼라', '주가하락']</t>
         </is>
       </c>
       <c r="X23" t="n">
